--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -577,12 +577,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2022-11-21, 2022-11-28, 2022-12-06, 2022-12-13, 2022-12-20, 2022-12-21, 2023-01-03, 2023-01-10, 2023-01-17, 2023-01-24, 2023-01-31, 2023-02-08, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-28, 2023-04-04, 2023-04-11, 2023-04-18, 2023-04-25, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-23, 2023-05-30, 2023-06-06, 2023-06-13, 2023-06-20, 2023-06-27, 2023-07-04, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-22, 2023-08-29, 2023-09-06, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-16, 2024-03-21, 2024-04-03, 2024-04-10, 2024-04-17, 2024-04-25, 2024-05-02, 2024-05-08, 2024-05-11, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-05, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-06, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-02, 2024-09-04, 2024-09-12, 2024-09-18, 2024-09-26, 2024-10-02, 2024-10-11, 2024-10-17, 2024-10-24, 2025-12-26, 2025-12-29, 2025-12-30, 2026-01-02, 2026-01-05, 2026-01-06, 2026-01-08, 2026-01-13, 2026-01-29, 2026-01-30, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18, 2026-03-03</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2022-11-25, 2022-12-01, 2022-12-09, 2022-12-14, 2022-12-21, 2022-12-28, 2023-01-04, 2023-01-11, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-07, 2023-09-13, 2023-09-20, 2023-09-28, 2023-10-05, 2023-10-11, 2023-10-18, 2023-10-26, 2023-11-02, 2023-11-09, 2023-11-16, 2023-11-25, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-21, 2024-01-04, 2024-01-11, 2024-01-19, 2024-01-29, 2024-02-02, 2024-02-09, 2024-02-17, 2024-02-23, 2024-03-01, 2024-03-08, 2024-03-18, 2024-03-22, 2024-04-04, 2024-04-13, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-08, 2024-05-11, 2024-05-17, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-05, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-30, 2024-09-02, 2024-09-06, 2024-09-16, 2024-09-20, 2024-09-28, 2024-10-03, 2024-10-16, 2024-10-18, 2024-10-25, 2025-12-26, 2025-12-29, 2026-01-02, 2026-01-05, 2026-01-06, 2026-01-08, 2026-01-13, 2026-01-29, 2026-01-30, 2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-03-03, 2026-03-04</t>
+          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -639,12 +639,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2025-12-23, 2025-12-26, 2026-01-06, 2026-01-23, 2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2025-12-26, 2026-01-06, 2026-01-23, 2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -699,11 +699,7 @@
       <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -791,12 +787,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2023-08-10, 2023-08-18, 2023-08-25, 2023-08-31, 2023-09-01, 2023-09-04, 2023-09-08, 2023-09-18, 2023-10-04, 2023-10-20, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-12, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-05, 2024-06-13, 2024-06-20, 2024-06-28, 2024-07-05, 2024-07-09, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-14, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-09, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-06, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-07, 2024-12-16, 2025-01-07, 2025-01-13, 2025-01-20, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-17, 2025-03-28, 2025-04-08, 2025-04-15, 2025-04-23, 2025-04-30, 2025-05-06, 2025-05-12, 2025-05-21, 2025-05-26, 2025-05-29, 2025-06-04, 2025-06-12, 2025-06-16, 2025-06-25, 2025-07-01, 2025-07-07, 2025-07-14, 2025-07-21, 2025-07-28, 2025-08-04, 2025-08-11, 2025-08-20, 2025-08-25, 2025-09-01, 2025-09-08, 2025-09-15, 2025-09-22, 2025-09-30, 2025-10-06, 2025-10-14, 2025-10-20, 2025-10-28, 2025-11-04, 2025-11-10, 2025-11-18, 2025-11-25, 2025-12-02, 2025-12-03, 2025-12-11, 2025-12-15, 2025-12-22, 2026-01-05, 2026-01-13, 2026-01-19, 2026-01-26, 2026-02-02, 2026-02-09, 2026-02-16, 2026-02-23, 2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-23</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2023-08-11, 2023-08-24, 2023-08-30, 2023-08-31, 2023-09-01, 2023-09-04, 2023-09-05, 2023-09-18, 2023-10-04, 2023-10-20, 2023-11-23, 2023-11-30, 2023-12-06, 2023-12-11, 2023-12-18, 2024-01-12, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-21, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-12, 2024-04-19, 2024-05-02, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-24, 2024-05-31, 2024-06-06, 2024-06-14, 2024-06-21, 2024-06-28, 2024-07-05, 2024-07-09, 2024-07-12, 2024-07-13, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-09, 2024-10-16, 2024-10-21, 2024-10-28, 2024-11-06, 2024-11-15, 2024-11-20, 2024-11-28, 2024-12-02, 2024-12-09, 2024-12-16, 2025-01-09, 2025-01-13, 2025-01-20, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-11, 2025-03-17, 2025-03-28, 2025-04-08, 2025-04-15, 2025-04-23, 2025-04-30, 2025-05-06, 2025-05-13, 2025-05-21, 2025-05-26, 2025-06-04, 2025-06-12, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-09, 2025-07-16, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-13, 2025-08-21, 2025-09-01, 2025-09-03, 2025-09-12, 2025-09-18, 2025-09-24, 2025-10-01, 2025-10-10, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-06, 2025-11-12, 2025-11-21, 2025-11-26, 2025-12-03, 2025-12-05, 2025-12-12, 2025-12-17, 2025-12-30, 2026-01-07, 2026-01-14, 2026-01-21, 2026-01-30, 2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25, 2026-03-04, 2026-03-11</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -861,12 +857,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2022-11-17, 2022-11-29, 2022-12-02, 2022-12-09, 2022-12-15, 2022-12-21, 2022-12-28, 2023-01-05, 2023-01-12, 2023-01-19, 2023-01-26, 2023-02-09, 2023-02-23, 2023-03-09, 2023-03-23, 2023-04-13, 2023-04-20, 2023-05-04, 2023-05-06, 2023-05-11, 2023-05-18, 2023-06-01, 2023-06-15, 2023-06-29, 2023-07-13, 2023-07-22, 2023-07-27, 2023-08-10, 2023-08-12, 2023-08-24, 2023-09-07, 2023-09-22, 2023-10-06, 2023-10-20, 2023-11-02, 2023-11-14, 2023-11-17, 2023-11-30, 2023-12-07, 2023-12-18, 2023-12-26, 2025-12-22, 2025-12-26, 2026-01-06, 2026-02-02, 2026-02-04, 2026-02-10, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25, 2026-03-02, 2026-03-03</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2022-11-28, 2022-12-02, 2022-12-09, 2022-12-16, 2022-12-22, 2022-12-29, 2023-01-06, 2023-01-14, 2023-01-21, 2023-01-27, 2023-02-10, 2023-02-25, 2023-03-11, 2023-03-25, 2023-04-15, 2023-04-22, 2023-05-06, 2023-05-12, 2023-05-20, 2023-06-03, 2023-06-17, 2023-07-01, 2023-07-15, 2023-07-24, 2023-07-29, 2023-08-12, 2023-08-19, 2023-08-26, 2023-09-09, 2023-09-23, 2023-10-07, 2023-10-20, 2023-11-07, 2023-11-14, 2023-11-17, 2023-11-30, 2023-12-07, 2023-12-18, 2025-12-22, 2025-12-26, 2026-01-06, 2026-02-02, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25, 2026-03-02, 2026-03-03</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -921,16 +917,8 @@
       <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>2021-12-28, 2021-12-29, 2022-01-06, 2022-01-11, 2022-01-18, 2022-01-25, 2022-02-01, 2022-02-08, 2022-02-11, 2022-02-16, 2022-02-23, 2022-02-28, 2022-03-09, 2022-03-10, 2022-03-15, 2022-03-22, 2022-03-30, 2022-04-06, 2022-04-13, 2022-04-20, 2022-04-28, 2022-05-07, 2022-05-18, 2022-05-19, 2022-05-24, 2022-06-02, 2022-06-08, 2022-06-17, 2022-06-22, 2022-06-28, 2022-07-05, 2022-07-12, 2022-07-19, 2022-07-26, 2022-08-02, 2022-08-09, 2022-08-16, 2022-08-23, 2022-08-30, 2022-09-06, 2022-09-13, 2022-09-20, 2022-09-27, 2022-10-04, 2022-10-11, 2022-10-18, 2022-10-25, 2022-11-01, 2022-11-08, 2022-11-15, 2022-11-22, 2022-11-29, 2022-12-06, 2022-12-13, 2022-12-20, 2022-12-27, 2023-01-03, 2023-01-10, 2023-01-17, 2023-01-23, 2023-01-30, 2023-02-06, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-28, 2023-04-04, 2023-04-11, 2023-04-18, 2023-04-25, 2023-05-02, 2023-05-09, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2024-01-04, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2025-11-27, 2025-11-28</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>2021-12-28, 2021-12-30, 2022-01-07, 2022-01-18, 2022-01-19, 2022-02-02, 2022-02-03, 2022-02-11, 2022-02-16, 2022-02-23, 2022-02-28, 2022-03-09, 2022-03-10, 2022-03-22, 2022-03-23, 2022-03-29, 2022-04-06, 2022-04-13, 2022-04-20, 2022-04-27, 2022-05-04, 2022-05-11, 2022-05-18, 2022-05-24, 2022-05-25, 2022-06-02, 2022-06-08, 2022-06-21, 2022-06-23, 2022-06-29, 2022-07-05, 2022-07-13, 2022-07-21, 2022-07-27, 2022-08-03, 2022-08-10, 2022-08-17, 2022-08-25, 2022-09-01, 2022-09-07, 2022-09-14, 2022-09-21, 2022-09-27, 2022-10-05, 2022-10-12, 2022-10-20, 2022-10-26, 2022-11-02, 2022-11-10, 2022-11-16, 2022-11-24, 2022-12-01, 2022-12-07, 2022-12-14, 2022-12-20, 2022-12-28, 2023-01-04, 2023-01-11, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-23, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-16, 2023-06-23, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-21, 2023-07-27, 2023-08-03, 2023-08-11, 2023-08-17, 2023-08-24, 2023-08-30, 2023-09-07, 2023-09-14, 2023-09-20, 2023-09-28, 2023-10-05, 2023-10-13, 2023-10-20, 2023-10-26, 2023-11-03, 2023-11-09, 2023-11-18, 2023-11-24, 2023-12-01, 2023-12-07, 2023-12-15, 2024-01-04, 2024-01-17, 2024-01-22, 2024-01-25, 2024-02-05, 2024-02-10, 2024-02-17, 2024-02-26, 2024-03-02, 2024-03-11, 2024-03-18, 2024-03-26, 2025-11-27, 2025-11-28</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
@@ -1017,12 +1005,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2024-08-12, 2024-08-13, 2024-10-01, 2024-10-15, 2024-10-21, 2024-11-01, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-09, 2024-12-16, 2025-01-07, 2025-01-13, 2025-01-20, 2025-01-27, 2025-02-07, 2025-02-17, 2025-03-05, 2025-03-10, 2025-03-17, 2025-03-25, 2025-03-31, 2025-04-08, 2025-04-14, 2025-04-21, 2025-04-28, 2025-05-05, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-03, 2025-06-09, 2025-06-14, 2025-06-25, 2025-07-02, 2025-07-07, 2025-07-14, 2025-07-18, 2025-07-31, 2025-08-04, 2025-08-11, 2025-08-25, 2025-09-01, 2025-09-08, 2025-09-15, 2025-09-23, 2025-09-29, 2025-10-06, 2025-10-08, 2025-10-20, 2025-10-27, 2025-11-06, 2025-11-10, 2025-11-19, 2025-11-24, 2025-12-01, 2025-12-10, 2025-12-15, 2025-12-22, 2026-01-14, 2026-01-19, 2026-01-27, 2026-02-02, 2026-02-09, 2026-02-16, 2026-02-25, 2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-25</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2024-08-20, 2024-10-15, 2024-10-17, 2024-11-01, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-09, 2024-12-16, 2025-01-07, 2025-01-13, 2025-01-20, 2025-01-27, 2025-02-07, 2025-02-17, 2025-03-05, 2025-03-07, 2025-03-10, 2025-03-17, 2025-03-25, 2025-04-03, 2025-04-08, 2025-04-15, 2025-04-23, 2025-04-30, 2025-05-05, 2025-05-14, 2025-05-21, 2025-05-26, 2025-06-05, 2025-06-11, 2025-06-20, 2025-06-25, 2025-07-02, 2025-07-10, 2025-07-18, 2025-07-21, 2025-07-31, 2025-08-08, 2025-08-12, 2025-08-25, 2025-09-02, 2025-09-08, 2025-09-18, 2025-09-23, 2025-09-29, 2025-10-06, 2025-10-16, 2025-10-21, 2025-10-30, 2025-11-06, 2025-11-10, 2025-11-19, 2025-11-28, 2025-12-03, 2025-12-11, 2025-12-18, 2026-01-14, 2026-01-22, 2026-01-29, 2026-02-04, 2026-02-13, 2026-02-19, 2026-02-26, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1121,12 +1109,12 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2024-10-18, 2024-10-21, 2024-10-23, 2024-10-30, 2024-11-06, 2024-11-13, 2024-11-20, 2024-11-27, 2024-12-04, 2024-12-11, 2024-12-18, 2025-01-10, 2025-01-16, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-17, 2025-03-25, 2025-03-31, 2025-04-07, 2025-04-21, 2025-04-28, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-05, 2025-06-12, 2025-06-20, 2025-07-03, 2025-07-10, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-19, 2025-09-26, 2025-10-07, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25, 2025-12-12, 2025-12-22, 2026-01-14, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26, 2026-03-03, 2026-03-10</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2024-10-21, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-30, 2024-12-07, 2024-12-13, 2024-12-20, 2025-01-10, 2025-01-20, 2025-02-07, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-11, 2025-03-18, 2025-03-26, 2025-04-01, 2025-04-09, 2025-04-25, 2025-05-06, 2025-05-19, 2025-05-20, 2025-06-05, 2025-06-06, 2025-06-20, 2025-07-03, 2025-07-04, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-25, 2025-09-02, 2025-09-06, 2025-09-15, 2025-09-19, 2025-09-26, 2025-10-08, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-05, 2025-11-12, 2025-11-19, 2025-11-26, 2025-12-13, 2026-01-08, 2026-01-15, 2026-01-22, 2026-01-29, 2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27, 2026-03-04</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1223,12 +1211,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2023-09-13, 2023-09-29, 2023-12-28, 2024-01-06, 2024-01-09, 2024-01-19, 2024-01-27, 2024-02-02, 2024-02-10, 2024-02-14, 2024-02-24, 2024-03-02, 2024-03-11, 2024-03-18, 2024-03-23, 2024-04-06, 2024-04-12, 2024-04-17, 2024-04-29, 2024-05-03, 2024-05-14, 2024-05-21, 2024-05-27, 2024-06-05, 2024-06-12, 2024-06-17, 2024-06-25, 2024-07-03, 2024-07-11, 2024-07-18, 2024-07-24, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-20, 2024-08-23, 2024-09-03, 2024-09-06, 2024-09-18, 2024-09-20, 2024-10-01, 2024-10-09, 2024-10-11, 2024-10-19, 2024-10-26, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-30, 2024-12-09, 2024-12-14, 2024-12-23, 2024-12-27, 2025-01-08, 2025-01-13, 2025-01-20, 2025-01-24, 2025-01-31, 2025-02-08, 2025-02-14, 2025-02-20, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-22, 2025-03-28, 2025-04-04, 2025-04-11, 2025-04-16, 2025-04-26, 2025-05-03, 2025-05-09, 2025-05-17, 2025-05-24, 2025-05-30, 2025-06-06, 2025-06-14, 2025-06-21, 2025-07-01, 2025-07-04, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-16, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-20, 2025-09-27, 2025-10-03, 2025-10-10, 2025-10-16, 2025-10-24, 2025-11-01, 2025-11-08, 2025-11-15, 2025-11-24, 2025-11-29, 2025-12-03, 2025-12-05, 2025-12-18, 2025-12-22, 2025-12-26, 2026-01-06, 2026-01-17, 2026-01-19, 2026-01-24, 2026-01-30, 2026-02-02, 2026-02-03, 2026-02-04, 2026-02-06, 2026-02-09, 2026-02-13, 2026-02-20, 2026-02-26, 2026-03-02, 2026-03-04, 2026-03-05</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-04, 2026-02-06, 2026-02-09, 2026-02-13, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2023-09-29, 2023-12-28, 2024-01-06, 2024-01-12, 2024-01-22, 2024-01-29, 2024-02-05, 2024-02-12, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-19, 2024-04-06, 2024-04-09, 2024-04-17, 2024-04-22, 2024-04-29, 2024-05-10, 2024-05-14, 2024-05-21, 2024-05-27, 2024-06-05, 2024-06-12, 2024-06-17, 2024-06-25, 2024-07-03, 2024-07-11, 2024-07-18, 2024-07-24, 2024-07-30, 2024-08-08, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-04, 2024-09-11, 2024-09-18, 2024-09-26, 2024-10-02, 2024-10-09, 2024-10-16, 2024-10-23, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-19, 2024-11-27, 2024-12-06, 2024-12-11, 2024-12-19, 2024-12-27, 2025-01-02, 2025-01-09, 2025-01-16, 2025-01-24, 2025-01-31, 2025-02-03, 2025-02-11, 2025-02-18, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-21, 2025-03-26, 2025-04-03, 2025-04-07, 2025-04-15, 2025-04-23, 2025-05-03, 2025-05-07, 2025-05-13, 2025-05-23, 2025-05-26, 2025-06-03, 2025-06-09, 2025-06-17, 2025-06-25, 2025-07-02, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-02, 2025-08-08, 2025-08-16, 2025-08-29, 2025-09-01, 2025-09-12, 2025-09-15, 2025-09-22, 2025-09-30, 2025-10-06, 2025-10-16, 2025-10-24, 2025-10-27, 2025-11-05, 2025-11-11, 2025-11-15, 2025-11-25, 2025-12-01, 2025-12-03, 2025-12-05, 2025-12-16, 2025-12-20, 2025-12-22, 2025-12-26, 2026-01-06, 2026-01-17, 2026-01-19, 2026-01-24, 2026-01-31, 2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-23, 2026-02-28, 2026-03-02, 2026-03-04, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-23, 2026-02-28</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1291,16 +1279,8 @@
       <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2023-08-15, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-12, 2024-01-09, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-13, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-11, 2024-03-19, 2024-04-02, 2024-04-11, 2024-04-12, 2024-04-23, 2024-05-03, 2024-05-07, 2024-05-14, 2024-05-22, 2024-05-28, 2024-06-07, 2024-06-12, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-25, 2024-07-29, 2024-07-31, 2024-08-06, 2024-08-15, 2024-08-16, 2024-08-17, 2024-08-25, 2024-08-27, 2024-09-01, 2024-09-05, 2024-09-12, 2024-09-18, 2024-09-26, 2024-10-04, 2024-10-24, 2024-11-01, 2024-11-08, 2024-11-14, 2024-11-15, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-26, 2024-12-27, 2025-01-13, 2025-01-16, 2025-01-17, 2025-01-23, 2025-01-27, 2025-01-30, 2025-02-10, 2025-02-20, 2025-03-10, 2025-03-17, 2025-03-19, 2025-03-31, 2025-04-01, 2025-04-02, 2025-04-10, 2025-04-21, 2025-04-23, 2025-04-24, 2025-04-28, 2025-05-10, 2025-05-19, 2025-05-21, 2025-05-22, 2025-06-18, 2025-06-19, 2025-07-04, 2025-07-07, 2025-07-10, 2025-07-11, 2025-07-14, 2025-07-17, 2025-07-28, 2025-07-31, 2025-08-04, 2025-08-05, 2025-08-08, 2025-08-14, 2025-08-19, 2025-08-29, 2025-09-02, 2025-09-05, 2025-09-08, 2025-09-20, 2025-10-10, 2025-10-24, 2025-11-10, 2025-11-14, 2025-11-27, 2026-03-09</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2023-08-15, 2023-08-22, 2023-08-29, 2023-09-12, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-15, 2024-03-20, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-03, 2024-05-08, 2024-05-16, 2024-05-24, 2024-05-30, 2024-06-07, 2024-06-13, 2024-06-20, 2024-06-28, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-25, 2024-07-26, 2024-07-29, 2024-08-01, 2024-08-09, 2024-08-16, 2024-08-17, 2024-08-22, 2024-08-25, 2024-08-30, 2024-09-01, 2024-09-06, 2024-09-12, 2024-09-20, 2024-09-27, 2024-10-05, 2024-10-28, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-28, 2024-12-05, 2024-12-26, 2024-12-27, 2025-01-16, 2025-01-17, 2025-01-23, 2025-01-30, 2025-02-07, 2025-02-19, 2025-02-24, 2025-03-11, 2025-03-18, 2025-03-19, 2025-04-01, 2025-04-02, 2025-04-07, 2025-04-10, 2025-04-23, 2025-04-24, 2025-04-30, 2025-05-10, 2025-05-21, 2025-05-22, 2025-06-19, 2025-06-20, 2025-07-04, 2025-07-07, 2025-07-10, 2025-07-11, 2025-07-17, 2025-07-24, 2025-07-29, 2025-08-04, 2025-08-05, 2025-08-06, 2025-08-08, 2025-08-14, 2025-08-19, 2025-08-29, 2025-09-04, 2025-09-05, 2025-09-08, 2025-09-22, 2025-10-10, 2025-10-24, 2025-11-10, 2025-11-14, 2026-03-06, 2026-03-09</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
@@ -1379,12 +1359,12 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2023-08-14, 2023-08-25, 2025-07-02, 2025-07-08, 2025-07-15, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-05, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-04, 2025-12-12, 2026-01-17, 2026-01-22, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-13, 2026-02-25, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-13, 2026-02-25, 2026-02-27</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2023-08-25, 2025-07-08, 2025-07-15, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-05, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-04, 2025-12-12, 2026-01-17, 2026-01-22, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1473,12 +1453,12 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2022-12-28, 2023-01-06, 2023-01-10, 2023-01-17, 2023-01-24, 2023-01-31, 2023-02-07, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-28, 2023-04-04, 2023-04-11, 2023-04-19, 2023-04-25, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-24, 2023-05-30, 2023-06-07, 2023-06-16, 2023-06-22, 2023-06-28, 2023-07-06, 2023-07-13, 2023-07-22, 2023-07-26, 2023-07-31, 2023-08-10, 2023-08-16, 2023-08-25, 2023-09-02, 2023-09-07, 2023-09-13, 2023-09-22, 2023-10-02, 2023-10-05, 2023-10-12, 2023-10-19, 2023-10-25, 2023-11-01, 2023-11-09, 2023-11-15, 2023-11-23, 2023-11-30, 2023-12-11, 2024-01-16, 2024-01-25, 2024-02-02, 2024-02-09, 2024-02-14, 2024-02-21, 2024-03-01, 2024-03-08, 2024-03-13, 2024-03-15, 2024-03-22, 2024-04-04, 2024-04-05, 2024-04-11, 2024-04-17, 2024-04-25, 2024-05-03, 2024-05-07, 2024-05-15, 2024-05-23, 2024-05-30, 2024-06-05, 2024-06-06, 2024-06-12, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-15, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-12, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-08, 2024-10-18, 2024-10-22, 2024-10-28, 2024-11-05, 2024-11-14, 2024-11-21, 2024-11-29, 2025-01-03, 2025-01-16, 2025-03-11, 2025-03-20, 2025-03-25, 2025-03-28, 2025-04-10, 2025-04-22, 2025-05-01, 2025-05-08, 2025-05-13, 2025-05-22, 2025-05-29, 2025-06-03, 2025-06-12, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-29, 2025-08-05, 2025-08-12, 2025-08-19, 2025-08-26, 2025-09-02, 2025-09-10, 2025-09-16, 2025-09-23, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2026-01-07, 2026-01-22, 2026-01-29, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-03</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2023-01-06, 2023-01-13, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-19, 2023-05-26, 2023-05-31, 2023-06-07, 2023-06-16, 2023-06-26, 2023-06-28, 2023-07-07, 2023-07-13, 2023-07-22, 2023-07-26, 2023-08-09, 2023-08-16, 2023-08-18, 2023-08-28, 2023-09-02, 2023-09-07, 2023-09-16, 2023-09-22, 2023-10-02, 2023-10-06, 2023-10-13, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-11, 2023-11-16, 2023-11-24, 2023-11-30, 2023-12-11, 2024-01-19, 2024-01-26, 2024-02-02, 2024-02-09, 2024-02-15, 2024-02-22, 2024-03-01, 2024-03-08, 2024-03-14, 2024-03-22, 2024-04-05, 2024-04-11, 2024-04-12, 2024-04-19, 2024-04-26, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-23, 2024-05-31, 2024-06-06, 2024-06-12, 2024-06-20, 2024-06-28, 2024-07-04, 2024-07-12, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-12, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-09, 2024-10-18, 2024-10-25, 2024-10-30, 2024-11-08, 2024-11-15, 2024-11-21, 2024-11-29, 2025-01-03, 2025-03-11, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-01, 2025-05-08, 2025-05-13, 2025-05-23, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-10, 2025-07-18, 2025-07-22, 2025-07-31, 2025-08-06, 2025-08-14, 2025-08-19, 2025-08-26, 2025-09-04, 2025-09-12, 2025-09-19, 2025-09-23, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2026-01-13, 2026-01-22, 2026-01-29, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-05</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1571,12 +1551,12 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2024-03-20, 2024-03-23, 2024-04-01, 2024-04-06, 2024-04-15, 2024-04-22, 2024-04-27, 2024-05-06, 2024-05-13, 2024-05-18, 2024-05-26, 2024-05-31, 2024-06-07, 2024-06-16, 2024-06-23, 2024-06-27, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-25, 2024-08-02, 2024-08-09, 2024-08-15, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-05, 2024-10-10, 2024-10-18, 2024-10-26, 2024-11-01, 2024-11-08, 2024-11-16, 2024-11-23, 2024-11-29, 2024-12-06, 2024-12-14, 2024-12-20, 2025-01-17, 2025-01-24, 2025-02-01, 2025-02-07, 2025-02-14, 2025-02-21, 2025-02-28, 2025-03-03, 2025-03-10, 2025-03-21, 2025-03-29, 2025-04-06, 2025-04-13, 2025-04-22, 2025-04-23, 2025-05-02, 2025-05-10, 2025-05-19, 2025-05-26, 2025-05-30, 2025-06-09, 2025-06-14, 2025-06-19, 2025-06-27, 2025-06-28, 2025-07-04, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-01, 2025-08-09, 2025-08-15, 2025-08-23, 2025-08-30, 2025-09-06, 2025-09-13, 2025-09-20, 2025-09-27, 2025-10-04, 2025-10-11, 2025-10-17, 2025-10-25, 2025-10-29, 2025-11-07, 2025-11-10, 2025-11-21, 2025-11-22, 2025-11-26, 2025-12-06, 2025-12-13, 2025-12-20, 2025-12-22, 2026-01-08, 2026-01-13, 2026-01-22, 2026-02-26, 2026-03-03, 2026-03-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2024-03-20, 2024-03-23, 2024-04-01, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-06, 2024-05-13, 2024-05-18, 2024-05-26, 2024-05-31, 2024-06-07, 2024-06-16, 2024-06-23, 2024-06-27, 2024-07-05, 2024-07-12, 2024-07-21, 2024-07-26, 2024-08-03, 2024-08-09, 2024-08-17, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-20, 2024-09-26, 2024-10-05, 2024-10-11, 2024-10-18, 2024-10-26, 2024-11-01, 2024-11-08, 2024-11-17, 2024-11-23, 2024-11-29, 2024-12-07, 2024-12-14, 2024-12-20, 2025-01-17, 2025-01-24, 2025-02-01, 2025-02-08, 2025-02-15, 2025-02-22, 2025-02-28, 2025-03-08, 2025-03-14, 2025-03-21, 2025-03-29, 2025-04-06, 2025-04-13, 2025-04-22, 2025-04-23, 2025-05-04, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-02, 2025-06-09, 2025-06-16, 2025-06-19, 2025-06-21, 2025-06-28, 2025-07-05, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-02, 2025-08-09, 2025-08-16, 2025-08-23, 2025-08-30, 2025-09-06, 2025-09-13, 2025-09-20, 2025-09-27, 2025-10-04, 2025-10-11, 2025-10-18, 2025-10-25, 2025-11-01, 2025-11-08, 2025-11-15, 2025-11-22, 2025-11-29, 2025-12-06, 2025-12-14, 2025-12-20, 2025-12-22, 2026-01-13, 2026-02-10, 2026-02-28, 2026-03-03, 2026-03-06</t>
+          <t>2026-02-10, 2026-02-28</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1639,16 +1619,8 @@
       <c r="P15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>2024-03-04, 2024-03-09, 2024-03-15, 2024-03-23, 2024-04-01, 2024-04-06, 2024-04-13, 2024-04-20, 2024-04-29, 2024-05-04, 2024-05-11, 2024-05-18, 2024-05-25, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-24, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-19, 2024-12-23, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-25, 2025-03-06, 2025-03-14, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-05-02, 2025-05-08, 2025-05-16, 2025-05-22, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-07, 2025-07-10, 2025-07-25, 2025-08-13, 2025-09-04, 2025-10-17, 2025-10-24, 2025-11-13, 2025-11-21</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2024-03-04, 2024-03-09, 2024-03-15, 2024-03-23, 2024-04-01, 2024-04-06, 2024-04-13, 2024-04-22, 2024-04-29, 2024-05-04, 2024-05-11, 2024-05-18, 2024-05-27, 2024-05-31, 2024-06-07, 2024-06-13, 2024-06-26, 2024-06-28, 2024-07-04, 2024-07-18, 2024-07-19, 2024-07-25, 2024-08-05, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-10-31, 2024-11-08, 2024-11-15, 2024-11-21, 2024-11-29, 2024-12-06, 2024-12-13, 2024-12-20, 2025-01-10, 2025-01-23, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-14, 2025-02-22, 2025-02-27, 2025-03-14, 2025-03-20, 2025-03-21, 2025-03-28, 2025-04-04, 2025-04-25, 2025-05-02, 2025-05-13, 2025-05-19, 2025-05-23, 2025-06-06, 2025-06-14, 2025-06-20, 2025-06-27, 2025-07-04, 2025-07-07, 2025-07-25, 2025-08-13, 2025-10-17, 2025-10-18, 2025-10-24, 2025-11-21</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
@@ -1703,12 +1675,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2023-11-14, 2023-11-16, 2023-11-21, 2023-11-28, 2023-12-07, 2023-12-15, 2024-01-12, 2024-01-18, 2024-01-25, 2024-02-02, 2024-02-10, 2024-02-15, 2024-02-23, 2024-03-08, 2024-03-14, 2024-03-21, 2024-04-01, 2024-04-06, 2024-04-12, 2024-04-20, 2024-04-27, 2024-05-04, 2024-05-11, 2024-05-18, 2024-05-26, 2024-06-01, 2024-06-08, 2024-06-15, 2024-06-21, 2024-07-02, 2024-07-13, 2024-07-21, 2024-07-25, 2024-08-01, 2024-08-09, 2024-08-15, 2024-08-23, 2024-08-30, 2024-09-09, 2024-09-13, 2024-09-24, 2024-09-26, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-30, 2024-12-06, 2024-12-14, 2024-12-27, 2025-01-24, 2025-02-02, 2025-02-08, 2025-02-13, 2025-02-22, 2025-03-01, 2025-03-03, 2025-03-14, 2025-03-17, 2025-03-30, 2025-04-06, 2025-04-13, 2025-04-23, 2025-05-04, 2025-05-11, 2025-05-18, 2025-05-25, 2025-06-01, 2025-06-05, 2025-06-13, 2025-06-21, 2025-06-27, 2025-07-05, 2025-07-12, 2025-07-21, 2025-07-27, 2025-08-09, 2025-08-16, 2025-08-24, 2025-08-29, 2025-09-13, 2025-09-17, 2025-09-18, 2025-09-19, 2025-09-24, 2025-09-29, 2025-10-07, 2025-10-16, 2025-10-17, 2025-10-26, 2025-10-28, 2025-11-06, 2025-11-15, 2025-11-19, 2025-11-29, 2026-02-05, 2026-02-28, 2026-03-02, 2026-03-03, 2026-03-04</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2023-11-14, 2023-11-17, 2023-11-23, 2023-12-01, 2023-12-07, 2023-12-15, 2024-01-14, 2024-01-19, 2024-01-26, 2024-02-02, 2024-02-10, 2024-02-15, 2024-02-23, 2024-03-01, 2024-03-09, 2024-03-15, 2024-03-21, 2024-04-01, 2024-04-06, 2024-04-20, 2024-04-27, 2024-05-05, 2024-05-11, 2024-05-18, 2024-05-26, 2024-06-01, 2024-06-08, 2024-06-15, 2024-06-21, 2024-07-02, 2024-07-13, 2024-07-21, 2024-07-26, 2024-08-03, 2024-08-09, 2024-08-17, 2024-08-26, 2024-08-31, 2024-09-09, 2024-09-14, 2024-09-24, 2024-09-27, 2024-10-05, 2024-10-11, 2024-10-19, 2024-10-25, 2024-11-01, 2024-11-09, 2024-11-16, 2024-11-23, 2024-12-01, 2024-12-07, 2024-12-14, 2025-01-18, 2025-01-25, 2025-02-03, 2025-02-08, 2025-02-15, 2025-02-23, 2025-03-01, 2025-03-09, 2025-03-14, 2025-03-22, 2025-03-30, 2025-04-08, 2025-04-13, 2025-04-26, 2025-05-04, 2025-05-11, 2025-05-18, 2025-05-25, 2025-06-02, 2025-06-08, 2025-06-13, 2025-06-21, 2025-06-27, 2025-07-05, 2025-07-13, 2025-07-21, 2025-08-02, 2025-08-09, 2025-08-16, 2025-08-24, 2025-08-30, 2025-09-13, 2025-09-17, 2025-09-18, 2025-09-19, 2025-09-24, 2025-09-29, 2025-10-07, 2025-10-16, 2025-10-17, 2025-10-27, 2025-10-28, 2025-11-06, 2025-11-15, 2025-11-19, 2025-11-29, 2026-02-05, 2026-02-28, 2026-03-02, 2026-03-03, 2026-03-04</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -1799,12 +1771,12 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2024-05-29, 2024-06-04, 2024-06-11, 2024-06-26, 2024-07-06, 2024-07-12, 2024-07-17, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2025-01-08, 2025-01-14, 2025-01-21, 2025-01-29, 2025-02-04, 2025-02-11, 2025-02-20, 2025-02-25, 2025-03-05, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-02, 2025-04-09, 2025-04-23, 2025-04-30, 2025-05-08, 2025-05-14, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-18, 2025-06-25, 2025-07-03, 2025-07-09, 2025-07-16, 2025-07-23, 2025-08-01, 2025-08-06, 2025-08-13, 2025-08-20, 2025-08-27, 2025-09-03, 2025-09-12, 2025-09-17, 2025-09-24, 2025-10-02, 2025-10-08, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-06, 2025-11-14, 2025-11-19, 2025-11-26, 2025-12-03, 2025-12-10, 2025-12-17, 2026-01-15, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-04, 2026-03-09</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2024-06-04, 2024-06-11, 2024-06-22, 2024-06-27, 2024-07-06, 2024-07-12, 2024-07-18, 2024-07-24, 2024-08-01, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-04, 2024-09-11, 2024-09-18, 2024-09-25, 2024-10-02, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-04, 2024-12-12, 2024-12-18, 2025-01-10, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-07, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-07, 2025-03-17, 2025-03-21, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-25, 2025-04-30, 2025-05-09, 2025-05-15, 2025-05-22, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-08-01, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-12, 2025-09-18, 2025-09-25, 2025-10-03, 2025-10-09, 2025-10-16, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-21, 2025-11-28, 2025-12-05, 2025-12-12, 2025-12-19, 2026-01-16, 2026-01-23, 2026-01-30, 2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27, 2026-03-06</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -1901,12 +1873,12 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2025-07-02, 2025-07-18, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-13, 2025-08-20, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-24, 2025-10-01, 2025-10-09, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-05, 2025-11-12, 2025-11-20, 2025-11-26, 2025-12-03, 2025-12-10, 2025-12-17, 2026-01-07, 2026-01-14, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-11</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2025-07-18, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-13, 2025-08-14, 2025-08-20, 2025-09-03, 2025-09-16, 2025-09-18, 2025-09-25, 2025-10-03, 2025-10-09, 2025-10-17, 2025-10-22, 2025-10-29, 2025-11-05, 2025-11-12, 2025-11-20, 2025-12-01, 2025-12-04, 2025-12-12, 2026-01-07, 2026-01-10, 2026-01-16, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -1995,12 +1967,12 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2022-11-29, 2022-12-16, 2022-12-20, 2022-12-28, 2023-01-13, 2023-01-18, 2023-01-24, 2023-01-31, 2023-02-07, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-29, 2023-04-04, 2023-04-11, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-16, 2023-05-24, 2023-05-30, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-04, 2023-07-11, 2023-07-19, 2023-07-25, 2023-08-01, 2023-08-09, 2023-08-16, 2023-08-22, 2023-08-29, 2023-09-05, 2024-10-16, 2024-11-05, 2025-01-16, 2025-01-23, 2025-01-24, 2025-02-05, 2025-02-10, 2025-02-19, 2025-02-26, 2025-03-05, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-09, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-06, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-06, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2026-01-07, 2026-01-22, 2026-01-27, 2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27, 2026-03-03</t>
+          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2022-12-12, 2022-12-19, 2022-12-26, 2022-12-29, 2023-01-13, 2023-01-19, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-11, 2023-04-13, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-22, 2023-06-29, 2023-07-05, 2023-07-15, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-10, 2023-08-16, 2023-08-23, 2023-08-31, 2023-09-05, 2024-11-05, 2025-01-16, 2025-01-23, 2025-01-24, 2025-02-10, 2025-02-21, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-09, 2025-05-22, 2025-05-29, 2025-06-07, 2025-06-12, 2025-06-20, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-06, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2026-01-13, 2026-01-22, 2026-01-27, 2026-02-04, 2026-02-12, 2026-02-20, 2026-02-27, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2063,16 +2035,8 @@
       <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>2023-10-23, 2023-11-10, 2023-12-07, 2023-12-15, 2024-02-05, 2024-02-12, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-05, 2024-04-08, 2024-04-23, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-19, 2025-01-07, 2025-01-14, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-07, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-11, 2025-03-17, 2025-03-19, 2025-03-25, 2025-04-02, 2025-04-03, 2025-04-23, 2025-04-29, 2025-05-08, 2025-05-13, 2025-05-21, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-18, 2025-06-24, 2025-07-02, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-30, 2025-08-06, 2025-08-14, 2025-08-20, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>2023-11-10, 2023-12-15, 2024-02-05, 2024-02-12, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-01, 2024-04-08, 2024-04-23, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-28, 2024-06-05, 2024-06-14, 2024-06-21, 2024-06-28, 2024-07-04, 2024-07-12, 2024-07-19, 2024-07-25, 2024-08-02, 2024-08-09, 2024-08-15, 2024-08-23, 2024-08-29, 2024-09-05, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-01, 2024-10-09, 2024-10-16, 2024-10-24, 2024-10-29, 2024-11-07, 2024-11-15, 2024-11-21, 2024-11-28, 2024-12-03, 2024-12-12, 2024-12-19, 2025-01-09, 2025-01-16, 2025-01-21, 2025-01-30, 2025-02-05, 2025-02-11, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-17, 2025-03-20, 2025-03-27, 2025-04-02, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-30, 2025-08-06, 2025-08-14, 2025-08-20, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09</t>
-        </is>
-      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="n">
@@ -2127,14 +2091,10 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2022-08-26, 2022-08-31, 2022-09-07, 2022-09-14, 2022-09-21, 2022-09-28, 2022-10-05, 2022-10-12, 2022-10-19, 2022-10-26, 2022-11-02, 2022-11-09, 2022-11-16, 2022-11-28, 2022-12-05, 2022-12-13, 2022-12-26, 2023-01-03, 2023-01-10, 2023-01-27, 2023-01-30, 2023-02-06, 2023-02-13, 2023-02-21, 2023-02-27, 2023-03-06, 2023-03-13, 2023-03-21, 2023-03-27, 2023-04-03, 2023-04-10, 2023-04-20, 2023-04-24, 2023-05-02, 2023-05-08, 2023-05-16, 2023-05-23, 2023-05-30, 2023-06-06, 2023-06-08, 2023-06-20, 2023-06-27, 2023-07-04, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-19, 2023-08-29, 2023-08-30, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-22, 2023-11-28, 2023-12-05, 2023-12-12, 2023-12-19, 2024-01-09, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-13, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-13, 2024-03-19, 2024-04-02, 2024-04-10, 2024-04-16, 2024-04-23, 2024-04-30, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-09, 2024-09-16, 2024-09-24, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-06, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-05, 2024-12-09, 2024-12-16, 2024-12-27, 2025-01-13, 2025-01-20, 2025-01-27, 2025-01-28, 2025-01-29, 2025-02-05, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-04, 2025-03-06, 2025-03-10, 2025-03-17, 2025-03-25, 2025-04-01, 2025-04-07, 2025-04-21, 2025-04-28, 2025-05-06, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-05, 2025-06-10, 2025-06-17, 2025-06-26, 2025-07-01, 2025-07-07, 2025-07-14, 2025-07-21, 2025-07-30, 2025-07-31, 2025-08-04, 2025-08-08, 2025-08-09, 2025-08-13, 2025-08-22, 2025-08-25, 2025-08-27, 2025-09-09, 2025-09-12, 2025-09-17, 2025-09-25, 2025-10-02, 2025-11-19, 2026-02-11</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>2022-08-26, 2022-08-31, 2022-09-07, 2022-09-14, 2022-09-21, 2022-09-28, 2022-10-05, 2022-10-12, 2022-10-19, 2022-10-26, 2022-11-02, 2022-11-09, 2022-11-16, 2022-11-29, 2022-12-05, 2022-12-13, 2023-01-03, 2023-01-10, 2023-01-27, 2023-01-30, 2023-01-31, 2023-02-07, 2023-02-14, 2023-02-27, 2023-02-28, 2023-03-13, 2023-03-14, 2023-03-21, 2023-03-29, 2023-04-05, 2023-04-11, 2023-04-21, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-24, 2023-05-30, 2023-06-06, 2023-06-13, 2023-06-20, 2023-06-27, 2023-07-04, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-26, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-08, 2024-02-16, 2024-02-22, 2024-03-01, 2024-03-06, 2024-03-13, 2024-03-21, 2024-04-03, 2024-04-11, 2024-04-17, 2024-04-25, 2024-05-03, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-07, 2024-06-12, 2024-06-20, 2024-06-27, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-30, 2024-09-04, 2024-09-11, 2024-09-19, 2024-09-25, 2024-10-02, 2024-10-09, 2024-10-16, 2024-10-23, 2024-10-31, 2024-11-08, 2024-11-15, 2024-11-20, 2024-11-28, 2024-12-04, 2024-12-05, 2024-12-11, 2024-12-19, 2025-01-10, 2025-01-17, 2025-01-21, 2025-01-27, 2025-01-28, 2025-01-29, 2025-02-07, 2025-02-12, 2025-02-19, 2025-02-27, 2025-03-04, 2025-03-06, 2025-03-12, 2025-03-19, 2025-03-27, 2025-04-02, 2025-04-09, 2025-04-24, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-21, 2025-05-28, 2025-06-05, 2025-06-12, 2025-06-18, 2025-06-26, 2025-07-02, 2025-07-10, 2025-07-17, 2025-07-23, 2025-07-30, 2025-07-31, 2025-08-04, 2025-08-08, 2025-08-09, 2025-08-13, 2025-08-22, 2025-08-25, 2025-08-27, 2025-09-09, 2025-09-12, 2025-09-17, 2025-09-25, 2025-10-09, 2025-11-20, 2026-03-06</t>
-        </is>
-      </c>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="n">
@@ -2221,12 +2181,12 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-23, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-27, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-07, 2024-03-13, 2024-03-20, 2024-03-27, 2024-04-03, 2024-04-10, 2024-04-17, 2024-04-24, 2024-05-02, 2024-05-09, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-28, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-16, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-20, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2024-12-23, 2025-01-07, 2025-01-10, 2025-01-13, 2025-01-14, 2025-01-22, 2025-01-29, 2025-02-05, 2025-02-12, 2025-02-19, 2025-02-26, 2025-03-05, 2025-03-12, 2025-03-19, 2025-03-26, 2025-04-03, 2025-04-09, 2025-04-16, 2025-04-23, 2025-04-30, 2025-05-02, 2025-05-07, 2025-05-14, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-10, 2025-07-16, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-11, 2025-08-26, 2025-08-27, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-24, 2025-10-01, 2025-10-08, 2025-10-15, 2025-10-21, 2025-10-29, 2025-11-04, 2025-11-17, 2025-11-19, 2025-11-26, 2025-12-05, 2025-12-10, 2025-12-22, 2025-12-27, 2025-12-29, 2026-01-07, 2026-01-15, 2026-01-21, 2026-01-28, 2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-14, 2026-02-16, 2026-02-18, 2026-02-20, 2026-02-24, 2026-02-25, 2026-03-04</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-14, 2026-02-16, 2026-02-18, 2026-02-20, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-21, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-18, 2023-08-24, 2023-09-02, 2023-09-07, 2023-09-15, 2023-09-21, 2023-09-28, 2023-10-05, 2023-10-13, 2023-10-19, 2023-10-27, 2023-11-02, 2023-11-09, 2023-11-16, 2023-11-23, 2023-12-01, 2023-12-07, 2023-12-14, 2023-12-21, 2024-01-02, 2024-01-05, 2024-01-12, 2024-01-19, 2024-01-25, 2024-02-02, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-20, 2024-03-27, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-30, 2024-05-02, 2024-05-11, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-20, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-19, 2025-01-07, 2025-01-10, 2025-01-13, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-14, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-04, 2025-04-10, 2025-04-23, 2025-04-24, 2025-05-02, 2025-05-07, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-11, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-26, 2025-08-28, 2025-09-10, 2025-09-11, 2025-09-23, 2025-09-25, 2025-10-03, 2025-10-09, 2025-10-20, 2025-10-24, 2025-10-30, 2025-11-04, 2025-11-17, 2025-11-20, 2025-12-05, 2025-12-13, 2025-12-22, 2025-12-27, 2026-01-07, 2026-01-13, 2026-01-21, 2026-01-27, 2026-01-30, 2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25, 2026-03-09</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2289,16 +2249,8 @@
       <c r="P23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>2022-08-09, 2022-08-18, 2022-08-23, 2022-08-31, 2022-09-06, 2022-09-15, 2022-09-20, 2022-09-28, 2022-10-04, 2022-10-11, 2022-10-18, 2022-10-24, 2022-10-31, 2022-11-08, 2022-11-15, 2022-11-22, 2022-11-28, 2022-12-06, 2022-12-13, 2022-12-19, 2022-12-27, 2023-01-04, 2023-01-10, 2023-01-18, 2023-01-24, 2023-01-30, 2023-02-08, 2023-02-16, 2023-02-22, 2023-03-03, 2023-03-08, 2023-03-13, 2023-03-21, 2023-03-27, 2023-04-03, 2023-04-10, 2023-04-24, 2023-05-02, 2023-05-08, 2023-05-15, 2023-05-23, 2023-05-30, 2023-06-05, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-22, 2023-08-28, 2023-09-06, 2023-09-11, 2023-09-18, 2023-09-26, 2023-10-02, 2023-10-09, 2023-10-17, 2023-10-22, 2023-10-30, 2023-11-06, 2023-11-14, 2023-11-23, 2023-11-27, 2023-12-05, 2023-12-11, 2023-12-27, 2024-01-09, 2024-01-15, 2024-01-24, 2024-01-29, 2024-02-05, 2024-02-14, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-01, 2024-04-13, 2024-04-17, 2024-04-23, 2024-04-29, 2024-05-03, 2024-05-04, 2024-05-05, 2024-05-17, 2024-05-21, 2024-05-27, 2024-05-30, 2024-06-12, 2024-06-15, 2024-06-17, 2024-06-28, 2024-07-04, 2024-07-13, 2024-07-15, 2024-07-19, 2024-07-22, 2024-07-25, 2024-07-29, 2024-08-05, 2024-08-09, 2024-08-10, 2024-08-12, 2024-08-14, 2024-08-17, 2024-08-22, 2024-08-24, 2024-08-29, 2024-09-02, 2024-09-06, 2024-09-07, 2024-09-14, 2024-09-20, 2024-09-23, 2024-10-16, 2024-10-24, 2024-10-29, 2024-11-01, 2025-02-24, 2025-03-05</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>2022-08-09, 2022-08-18, 2022-08-23, 2022-09-02, 2022-09-07, 2022-09-19, 2022-09-20, 2022-09-30, 2022-10-05, 2022-10-12, 2022-10-19, 2022-10-26, 2022-11-02, 2022-11-08, 2022-11-15, 2022-11-23, 2022-11-30, 2022-12-07, 2022-12-14, 2022-12-21, 2022-12-28, 2023-01-06, 2023-01-12, 2023-01-19, 2023-01-31, 2023-02-02, 2023-02-13, 2023-02-16, 2023-02-24, 2023-03-07, 2023-03-09, 2023-03-15, 2023-03-23, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-27, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-08, 2023-07-15, 2023-07-21, 2023-08-02, 2023-08-09, 2023-08-18, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-16, 2023-09-20, 2023-09-29, 2023-10-06, 2023-10-17, 2023-10-18, 2023-10-30, 2023-11-01, 2023-11-08, 2023-11-17, 2023-11-27, 2023-11-30, 2023-12-08, 2023-12-14, 2023-12-28, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-09, 2024-02-16, 2024-02-23, 2024-03-01, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-15, 2024-04-18, 2024-04-26, 2024-05-02, 2024-05-04, 2024-05-05, 2024-05-09, 2024-05-17, 2024-05-21, 2024-05-28, 2024-05-30, 2024-06-12, 2024-06-15, 2024-06-17, 2024-06-28, 2024-07-04, 2024-07-13, 2024-07-18, 2024-07-19, 2024-07-22, 2024-07-25, 2024-07-27, 2024-08-01, 2024-08-05, 2024-08-08, 2024-08-09, 2024-08-10, 2024-08-13, 2024-08-14, 2024-08-17, 2024-08-22, 2024-08-28, 2024-08-29, 2024-09-03, 2024-09-06, 2024-09-12, 2024-09-20, 2024-10-02, 2024-10-16, 2024-10-24, 2024-10-29, 2024-11-01, 2025-03-05</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="n">
@@ -2351,16 +2303,8 @@
       <c r="P24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>2022-08-03, 2022-08-09, 2022-08-18, 2022-08-23, 2022-08-30, 2022-09-06, 2022-09-15, 2022-09-20, 2022-09-27, 2022-10-04, 2022-10-11, 2022-10-18, 2022-10-24, 2022-10-31, 2022-11-08, 2022-11-15, 2022-11-21, 2022-11-28, 2022-12-05, 2022-12-13, 2022-12-19, 2022-12-27, 2023-01-04, 2023-01-10, 2023-01-16, 2023-01-24, 2023-01-31, 2023-02-08, 2023-02-15, 2023-02-22, 2023-02-28, 2023-03-08, 2023-03-13, 2023-03-21, 2023-03-27, 2023-04-03, 2023-04-10, 2023-04-24, 2023-05-02, 2023-05-08, 2023-05-15, 2023-05-23, 2023-05-30, 2023-06-05, 2023-06-14, 2023-06-21, 2023-06-27, 2023-07-05, 2023-07-10, 2023-07-19, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-11, 2023-09-18, 2023-09-25, 2023-10-02, 2023-10-09, 2023-10-17, 2023-10-24, 2023-10-30, 2023-11-07, 2023-11-14, 2023-11-24, 2023-12-04, 2023-12-11, 2023-12-18, 2023-12-26, 2024-01-02, 2024-01-09, 2024-01-15, 2024-01-22, 2024-01-29, 2024-02-07, 2024-02-12, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-04, 2024-04-08, 2024-04-15, 2024-04-23, 2024-04-29, 2024-05-03, 2024-05-05, 2024-05-17, 2024-05-21, 2024-05-27, 2024-05-30, 2024-06-12, 2024-06-13, 2024-06-17, 2024-06-28, 2024-07-04, 2024-07-13, 2024-07-15, 2024-07-22, 2024-07-29, 2024-07-30, 2024-08-05, 2024-08-12, 2024-08-23, 2024-08-30, 2024-09-04, 2024-09-13, 2024-09-25, 2024-10-29, 2025-02-24, 2025-03-05</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>2022-08-05, 2022-08-09, 2022-08-18, 2022-08-23, 2022-09-01, 2022-09-07, 2022-09-19, 2022-09-20, 2022-09-30, 2022-10-05, 2022-10-12, 2022-10-19, 2022-10-26, 2022-11-02, 2022-11-08, 2022-11-15, 2022-11-23, 2022-11-30, 2022-12-07, 2022-12-14, 2022-12-21, 2022-12-28, 2023-01-06, 2023-01-12, 2023-01-18, 2023-01-26, 2023-02-02, 2023-02-13, 2023-02-16, 2023-02-24, 2023-03-03, 2023-03-09, 2023-03-15, 2023-03-23, 2023-03-30, 2023-04-05, 2023-04-12, 2023-04-27, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-25, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-08, 2023-07-15, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-08, 2023-09-18, 2023-09-25, 2023-10-02, 2023-10-09, 2023-10-16, 2023-10-20, 2023-10-26, 2023-11-02, 2023-11-13, 2023-11-15, 2023-11-29, 2023-12-07, 2023-12-18, 2023-12-20, 2023-12-28, 2024-01-03, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-09, 2024-02-14, 2024-02-22, 2024-03-01, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-13, 2024-04-18, 2024-04-26, 2024-05-02, 2024-05-05, 2024-05-09, 2024-05-17, 2024-05-21, 2024-05-28, 2024-05-30, 2024-06-12, 2024-06-13, 2024-06-17, 2024-06-28, 2024-07-04, 2024-07-13, 2024-07-17, 2024-07-23, 2024-07-29, 2024-07-30, 2024-08-05, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-04, 2024-09-25, 2024-11-01, 2025-02-24, 2025-03-05</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="n">
@@ -2447,12 +2391,12 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2025-05-28, 2025-06-03, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-29, 2025-08-06, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-02, 2025-09-09, 2025-09-16, 2025-09-23, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-02, 2025-12-09, 2025-12-16, 2025-12-23, 2026-01-06, 2026-01-13, 2026-01-20, 2026-01-27, 2026-02-03, 2026-02-10, 2026-02-17, 2026-02-24, 2026-03-03, 2026-03-10</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2025-06-04, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-29, 2025-08-06, 2025-08-12, 2025-08-20, 2025-09-02, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-10, 2025-10-17, 2025-10-23, 2025-10-29, 2025-11-06, 2025-11-14, 2025-11-20, 2025-11-27, 2025-12-05, 2025-12-11, 2025-12-18, 2025-12-26, 2026-01-08, 2026-01-15, 2026-01-22, 2026-01-30, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2541,12 +2485,12 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2022-09-02, 2022-09-06, 2022-09-13, 2022-09-20, 2022-09-27, 2022-10-11, 2022-10-18, 2022-10-25, 2022-11-01, 2022-11-08, 2022-11-15, 2022-11-21, 2022-11-28, 2022-12-05, 2022-12-12, 2022-12-19, 2022-12-26, 2023-01-02, 2023-01-10, 2023-01-16, 2023-01-23, 2023-01-30, 2023-02-06, 2023-02-13, 2023-02-22, 2023-02-23, 2023-03-07, 2023-03-15, 2023-03-23, 2023-03-29, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-15, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-12, 2023-12-20, 2023-12-27, 2024-01-03, 2024-01-09, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-01, 2024-02-14, 2024-02-20, 2024-02-28, 2024-03-05, 2024-03-13, 2024-03-19, 2024-04-02, 2024-04-10, 2024-04-16, 2024-04-23, 2024-05-02, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-14, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-25, 2024-10-02, 2024-10-10, 2024-10-16, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2024-12-23, 2025-01-14, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-13, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-15, 2025-04-23, 2025-04-29, 2025-05-06, 2025-05-13, 2025-05-20, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-02, 2025-07-08, 2025-07-17, 2025-07-22, 2025-07-29, 2025-08-06, 2025-08-13, 2025-08-20, 2025-08-28, 2025-09-02, 2025-09-09, 2025-09-24, 2025-09-30, 2025-10-06, 2025-10-07, 2025-10-14, 2025-10-17, 2025-10-21, 2025-10-22, 2025-10-28, 2025-11-04, 2025-11-11, 2025-11-18, 2025-11-21, 2025-11-25, 2025-11-28, 2025-12-01, 2025-12-03, 2025-12-05, 2025-12-09, 2025-12-15, 2025-12-22, 2026-01-02, 2026-01-07, 2026-01-13, 2026-01-17, 2026-01-23, 2026-01-24, 2026-01-30, 2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26, 2026-03-04</t>
+          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2022-09-08, 2022-09-15, 2022-09-21, 2022-09-28, 2022-10-12, 2022-10-19, 2022-10-29, 2022-11-02, 2022-11-09, 2022-11-16, 2022-11-25, 2022-11-30, 2022-12-09, 2022-12-14, 2022-12-26, 2022-12-27, 2023-01-04, 2023-01-11, 2023-01-18, 2023-01-26, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-23, 2023-03-02, 2023-03-09, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-31, 2023-06-01, 2023-06-09, 2023-06-15, 2023-06-23, 2023-06-29, 2023-07-07, 2023-07-13, 2023-07-21, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-26, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-07, 2023-12-13, 2023-12-21, 2023-12-27, 2024-01-03, 2024-01-12, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-29, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-04, 2024-04-10, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-06, 2024-06-12, 2024-06-18, 2024-06-27, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-21, 2024-08-29, 2024-09-04, 2024-09-11, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-30, 2024-11-06, 2024-11-13, 2024-11-21, 2024-11-27, 2024-12-04, 2024-12-12, 2024-12-18, 2025-01-08, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-12, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-14, 2025-03-20, 2025-03-26, 2025-04-03, 2025-04-09, 2025-04-16, 2025-04-24, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-06, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-09, 2025-07-18, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-15, 2025-08-21, 2025-08-30, 2025-09-04, 2025-09-16, 2025-09-25, 2025-10-02, 2025-10-06, 2025-10-10, 2025-10-17, 2025-10-21, 2025-10-22, 2025-10-24, 2025-10-30, 2025-11-07, 2025-11-11, 2025-11-13, 2025-11-18, 2025-11-21, 2025-11-26, 2025-11-28, 2025-12-03, 2025-12-05, 2025-12-11, 2025-12-19, 2025-12-22, 2026-01-02, 2026-01-07, 2026-01-13, 2026-01-17, 2026-01-23, 2026-01-24, 2026-01-30, 2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26, 2026-03-04, 2026-03-06</t>
+          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -2611,12 +2555,12 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2022-11-22, 2022-11-30, 2022-12-06, 2022-12-13, 2022-12-20, 2022-12-28, 2023-01-03, 2023-01-10, 2023-01-17, 2023-01-24, 2023-01-31, 2023-02-08, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-28, 2023-04-04, 2023-04-11, 2023-04-18, 2023-04-25, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-23, 2023-05-30, 2023-06-06, 2023-06-13, 2023-06-20, 2023-06-27, 2023-07-04, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-05, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-12, 2023-12-19, 2023-12-26, 2024-01-02, 2024-01-09, 2024-01-12, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-13, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-12, 2024-03-19, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-23, 2024-04-30, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-12, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-27, 2024-12-03, 2024-12-10, 2025-01-09, 2025-09-26, 2025-10-08, 2025-10-14, 2025-10-28, 2025-10-31, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-02, 2025-12-09, 2025-12-16, 2026-01-13, 2026-01-30, 2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27, 2026-03-03, 2026-03-10</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2022-11-26, 2022-11-30, 2022-12-09, 2022-12-14, 2022-12-21, 2022-12-28, 2023-01-04, 2023-01-12, 2023-01-18, 2023-01-25, 2023-02-03, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-08, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-12, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-27, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-15, 2024-02-22, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-10, 2024-04-17, 2024-04-24, 2024-05-02, 2024-05-09, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-20, 2024-06-26, 2024-07-04, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-29, 2024-09-04, 2024-09-13, 2024-09-18, 2024-09-25, 2024-10-02, 2024-10-09, 2024-10-16, 2024-10-24, 2024-10-30, 2024-11-06, 2024-11-13, 2024-11-20, 2024-11-27, 2024-12-04, 2024-12-11, 2025-01-09, 2025-09-26, 2025-10-08, 2025-10-14, 2025-10-29, 2025-11-04, 2025-11-11, 2025-11-25, 2025-12-02, 2025-12-09, 2025-12-16, 2026-01-13, 2026-01-30, 2026-02-03, 2026-02-24, 2026-02-27, 2026-03-03, 2026-03-10</t>
+          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
@@ -2701,12 +2645,12 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2023-08-14, 2023-08-15, 2023-08-25, 2023-08-27, 2023-08-30, 2023-09-06, 2023-10-05, 2023-10-19, 2023-10-26, 2023-11-03, 2023-11-09, 2023-11-17, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-21, 2024-01-04, 2024-01-12, 2024-01-18, 2024-01-25, 2024-02-02, 2024-02-09, 2024-02-15, 2024-02-22, 2024-03-02, 2024-03-08, 2024-03-15, 2024-03-26, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-23, 2024-04-30, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-03, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2024-12-23, 2024-12-30, 2025-01-07, 2025-01-14, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-22, 2025-04-30, 2025-05-06, 2025-05-13, 2025-05-20, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-13, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-30, 2025-08-06, 2025-08-14, 2025-08-20, 2025-08-27, 2025-09-02, 2025-09-09, 2025-09-17, 2025-09-24, 2025-09-29, 2025-10-02, 2025-10-07, 2025-10-14, 2025-10-15, 2025-10-17, 2025-10-21, 2025-10-24, 2025-10-27, 2025-10-28, 2025-11-05, 2025-11-07, 2025-11-11, 2025-11-12, 2025-11-19, 2025-11-25, 2025-11-28, 2025-12-03, 2025-12-10, 2025-12-27, 2026-01-06, 2026-01-26, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2023-08-14, 2023-08-25, 2023-08-28, 2023-08-30, 2023-09-06, 2023-10-13, 2023-10-20, 2023-10-31, 2023-11-03, 2023-11-10, 2023-11-17, 2023-11-25, 2023-11-30, 2023-12-07, 2023-12-15, 2023-12-21, 2024-01-04, 2024-01-13, 2024-01-19, 2024-01-26, 2024-02-03, 2024-02-15, 2024-02-19, 2024-02-24, 2024-03-02, 2024-03-08, 2024-03-15, 2024-03-27, 2024-04-03, 2024-04-10, 2024-04-22, 2024-04-24, 2024-05-02, 2024-05-14, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-12, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-04, 2024-09-11, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-18, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-09, 2024-12-12, 2024-12-19, 2024-12-26, 2025-01-02, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-21, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-05, 2025-05-08, 2025-05-16, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-08-01, 2025-08-08, 2025-08-14, 2025-08-27, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-15, 2025-10-17, 2025-10-24, 2025-10-27, 2025-10-31, 2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-20, 2025-11-27, 2025-11-28, 2025-12-03, 2025-12-04, 2025-12-12, 2025-12-27, 2026-01-09, 2026-01-30, 2026-02-06, 2026-02-13, 2026-02-20, 2026-03-05</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -2769,16 +2713,8 @@
       <c r="P29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>2022-11-23, 2022-11-30, 2022-12-07, 2022-12-14, 2022-12-21, 2022-12-29, 2023-01-04, 2023-01-11, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-04, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-10, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-27, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-03-27, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-06, 2024-05-14, 2024-05-20, 2024-05-27, 2024-06-04, 2024-06-11, 2024-06-17, 2024-06-24, 2024-07-02, 2024-07-08, 2024-07-15, 2024-07-22, 2024-07-29, 2024-08-05, 2024-08-12, 2024-08-20, 2024-08-26, 2024-09-02, 2024-09-09, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-05, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-09, 2024-12-16, 2025-01-07, 2025-01-14, 2025-01-20, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-17, 2025-03-25, 2025-03-31, 2025-04-07, 2025-04-14, 2025-04-21, 2025-04-28, 2025-05-05, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-03, 2025-06-09, 2025-06-16, 2025-06-24, 2025-07-01, 2025-07-07, 2025-07-14, 2025-07-21, 2025-07-28, 2025-08-04, 2025-08-12, 2025-08-19, 2025-08-25, 2025-09-01, 2025-09-08, 2025-09-15, 2025-09-23, 2025-09-29, 2025-10-08, 2025-10-21, 2025-10-29, 2025-11-04, 2025-11-10, 2025-11-18, 2025-11-24, 2025-12-09, 2025-12-18, 2025-12-23, 2025-12-29, 2026-01-07, 2026-01-14</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>2022-11-24, 2022-12-01, 2022-12-09, 2022-12-15, 2022-12-22, 2022-12-29, 2023-01-05, 2023-01-12, 2023-01-19, 2023-01-26, 2023-02-02, 2023-02-09, 2023-02-16, 2023-02-23, 2023-03-03, 2023-03-10, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-05, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-21, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-08-31, 2023-09-07, 2023-09-14, 2023-09-21, 2023-09-28, 2023-10-05, 2023-10-12, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-10, 2023-11-16, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-21, 2024-01-03, 2024-01-04, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-01, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-06, 2024-05-14, 2024-05-20, 2024-05-27, 2024-06-04, 2024-06-11, 2024-06-17, 2024-06-24, 2024-07-02, 2024-07-08, 2024-07-15, 2024-07-22, 2024-07-29, 2024-08-12, 2024-08-20, 2024-08-26, 2024-09-02, 2024-09-09, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-05, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-09, 2024-12-17, 2025-01-07, 2025-01-14, 2025-01-20, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-17, 2025-03-25, 2025-03-31, 2025-04-07, 2025-04-14, 2025-04-21, 2025-04-28, 2025-05-05, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-03, 2025-06-09, 2025-06-16, 2025-06-24, 2025-07-01, 2025-07-07, 2025-07-15, 2025-07-21, 2025-07-28, 2025-08-06, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-03, 2025-09-08, 2025-09-16, 2025-09-23, 2025-09-30, 2025-10-08, 2025-10-21, 2025-10-29, 2025-11-04, 2025-11-12, 2025-11-18, 2025-11-24, 2025-12-09, 2025-12-18, 2025-12-23, 2025-12-29, 2026-01-07, 2026-01-14</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="n">
@@ -2865,12 +2801,12 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2022-12-22, 2022-12-29, 2023-01-05, 2023-01-12, 2023-01-19, 2023-01-26, 2023-02-03, 2023-02-09, 2023-02-16, 2023-02-23, 2023-03-02, 2023-03-09, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-17, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-14, 2023-08-22, 2023-08-28, 2023-09-05, 2023-09-11, 2023-09-19, 2023-09-26, 2023-10-02, 2023-10-09, 2023-10-17, 2023-10-24, 2023-10-30, 2023-11-08, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-11, 2023-12-19, 2023-12-27, 2024-01-03, 2024-01-09, 2024-01-15, 2024-01-22, 2024-01-29, 2024-02-05, 2024-02-12, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-01, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-06, 2024-05-14, 2024-05-20, 2024-05-27, 2024-06-04, 2024-06-11, 2024-06-17, 2024-06-24, 2024-07-03, 2024-07-08, 2024-07-10, 2024-07-22, 2024-07-29, 2024-08-05, 2024-08-12, 2024-08-20, 2024-08-27, 2024-09-02, 2024-09-09, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-08, 2024-12-03, 2024-12-10, 2025-01-03, 2025-01-17, 2025-03-13, 2025-05-29, 2025-06-19, 2025-07-07, 2025-07-14, 2025-07-23, 2025-07-31, 2025-08-06, 2025-08-12, 2025-08-29, 2025-09-11, 2025-09-16, 2025-09-22, 2025-10-04, 2025-10-09, 2025-10-15, 2025-10-23, 2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-24, 2025-12-02, 2025-12-04, 2025-12-10, 2025-12-17, 2026-01-14, 2026-01-19, 2026-01-20, 2026-01-26, 2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24, 2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2022-12-26, 2022-12-29, 2023-01-06, 2023-01-13, 2023-01-20, 2023-01-27, 2023-02-03, 2023-02-10, 2023-02-17, 2023-02-24, 2023-03-03, 2023-03-10, 2023-03-17, 2023-03-24, 2023-03-31, 2023-04-14, 2023-04-21, 2023-04-28, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-10, 2023-06-16, 2023-06-23, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-18, 2023-07-25, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-29, 2023-09-05, 2023-09-12, 2023-09-20, 2023-09-26, 2023-10-03, 2023-10-13, 2023-10-17, 2023-10-25, 2023-10-31, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-12, 2023-12-19, 2023-12-27, 2024-01-05, 2024-01-10, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-14, 2024-02-22, 2024-03-01, 2024-03-07, 2024-03-12, 2024-03-19, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-23, 2024-04-30, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-28, 2024-06-05, 2024-06-12, 2024-06-18, 2024-06-25, 2024-07-03, 2024-07-10, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-14, 2024-08-23, 2024-08-29, 2024-09-03, 2024-09-11, 2024-09-17, 2024-09-24, 2024-10-02, 2024-10-09, 2024-10-17, 2024-10-25, 2024-10-30, 2024-11-26, 2024-12-03, 2024-12-10, 2025-01-03, 2025-01-17, 2025-03-14, 2025-05-30, 2025-07-07, 2025-07-14, 2025-07-28, 2025-07-31, 2025-08-06, 2025-08-15, 2025-09-05, 2025-09-11, 2025-09-16, 2025-09-23, 2025-10-04, 2025-10-09, 2025-10-15, 2025-10-23, 2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-24, 2025-12-02, 2025-12-04, 2025-12-10, 2025-12-17, 2026-01-14, 2026-01-19, 2026-01-20, 2026-01-26, 2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24, 2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -2933,16 +2869,8 @@
       <c r="P31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>2022-11-17, 2022-12-01, 2022-12-15, 2023-02-03, 2023-02-10, 2023-02-16, 2023-02-23, 2023-03-01, 2023-03-07, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-23, 2023-06-29, 2023-07-07, 2023-07-14, 2023-07-21, 2023-07-28, 2023-08-04, 2023-08-11, 2023-08-17, 2023-08-25, 2023-08-31, 2023-09-08, 2023-09-15, 2023-09-21, 2023-09-28, 2023-10-06, 2023-10-13, 2023-10-20, 2023-10-27, 2023-11-16, 2023-11-23, 2023-11-30, 2023-12-07, 2024-12-23</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>2022-11-24, 2022-12-01, 2023-02-02, 2023-02-03, 2023-02-13, 2023-02-17, 2023-02-24, 2023-03-03, 2023-03-11, 2023-03-17, 2023-03-25, 2023-03-31, 2023-04-14, 2023-04-27, 2023-04-28, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-09, 2023-06-16, 2023-06-26, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-21, 2023-08-02, 2023-08-05, 2023-08-11, 2023-08-25, 2023-09-01, 2023-09-08, 2023-09-15, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-25, 2023-10-27, 2023-11-17, 2023-11-24, 2023-12-06, 2024-02-02</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="n">
@@ -3029,12 +2957,12 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2023-03-14, 2023-03-21, 2023-03-28, 2023-04-03, 2023-04-10, 2023-04-24, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-23, 2023-05-30, 2023-06-06, 2023-06-13, 2023-06-20, 2023-06-27, 2023-07-05, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-09, 2023-08-14, 2023-08-22, 2023-08-28, 2023-09-04, 2023-09-11, 2023-09-18, 2023-09-25, 2023-10-02, 2023-10-09, 2023-10-17, 2023-10-23, 2023-10-30, 2023-11-07, 2023-11-14, 2023-11-20, 2023-11-27, 2023-12-04, 2023-12-11, 2023-12-18, 2024-01-09, 2024-01-15, 2024-01-22, 2024-01-29, 2024-02-05, 2024-02-12, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-01, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-07, 2024-05-14, 2024-05-20, 2024-05-27, 2024-06-04, 2024-06-11, 2024-06-17, 2024-06-24, 2024-07-02, 2024-07-08, 2024-07-15, 2024-07-22, 2024-07-29, 2024-08-05, 2024-08-12, 2024-08-20, 2024-08-23, 2024-09-02, 2024-09-10, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-08, 2024-10-15, 2024-10-21, 2024-10-25, 2024-11-05, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-10, 2024-12-17, 2024-12-27, 2025-01-14, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-23, 2025-04-29, 2025-05-06, 2025-05-13, 2025-05-20, 2025-05-28, 2025-06-03, 2025-06-10, 2025-06-18, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-23, 2025-07-29, 2025-08-05, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-02, 2025-09-09, 2025-09-16, 2025-09-23, 2025-10-01, 2025-10-09, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-12, 2025-11-20, 2025-11-26, 2025-12-03, 2025-12-09, 2025-12-18, 2026-01-14, 2026-01-20, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-03</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-13, 2023-04-26, 2023-05-04, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-26, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-09, 2024-04-17, 2024-04-24, 2024-04-30, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-06, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-05, 2024-09-12, 2024-09-18, 2024-09-25, 2024-10-02, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-27, 2024-12-05, 2024-12-12, 2024-12-19, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-21, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2026-01-15, 2026-01-21, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3099,12 +3027,12 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2022-12-07, 2022-12-15, 2022-12-22, 2022-12-29, 2023-01-05, 2023-01-12, 2023-01-19, 2023-01-26, 2023-02-02, 2023-02-09, 2023-02-16, 2023-02-23, 2023-03-02, 2023-03-09, 2023-03-11, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-18, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-08-31, 2023-09-07, 2023-09-14, 2023-09-21, 2023-09-28, 2023-10-05, 2023-10-12, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-04, 2023-11-15, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-21, 2023-12-28, 2024-01-04, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-05, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-10, 2024-03-17, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-03, 2024-05-08, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-15, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-26, 2024-08-28, 2024-09-04, 2024-09-11, 2024-09-18, 2024-09-26, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-31, 2024-11-05, 2024-11-11, 2024-11-16, 2024-11-28, 2024-12-03, 2024-12-10, 2025-01-09, 2025-01-14, 2025-01-21, 2025-01-30, 2025-02-07, 2025-02-14, 2025-02-22, 2025-03-01, 2025-03-18, 2025-04-12, 2025-04-24, 2025-06-19, 2025-12-26, 2025-12-30, 2026-01-02, 2026-01-05, 2026-01-09, 2026-01-13, 2026-01-20, 2026-01-21, 2026-01-22, 2026-01-26, 2026-01-27, 2026-01-28, 2026-01-31, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16, 2026-02-17, 2026-03-02, 2026-03-03</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16, 2026-02-17</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2022-12-09, 2022-12-16, 2022-12-22, 2022-12-30, 2023-01-06, 2023-01-13, 2023-01-20, 2023-01-27, 2023-02-03, 2023-02-10, 2023-02-17, 2023-02-24, 2023-03-03, 2023-03-10, 2023-03-17, 2023-03-24, 2023-03-31, 2023-04-14, 2023-04-21, 2023-04-29, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-10, 2023-06-20, 2023-06-26, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-21, 2023-07-28, 2023-08-04, 2023-08-11, 2023-08-18, 2023-08-25, 2023-09-01, 2023-09-08, 2023-09-16, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-20, 2023-10-27, 2023-11-03, 2023-11-10, 2023-11-17, 2023-11-24, 2023-12-01, 2023-12-07, 2023-12-16, 2023-12-21, 2023-12-28, 2024-01-05, 2024-01-13, 2024-01-19, 2024-01-26, 2024-02-02, 2024-02-09, 2024-02-17, 2024-02-23, 2024-03-03, 2024-03-08, 2024-03-16, 2024-04-04, 2024-04-05, 2024-04-12, 2024-04-19, 2024-04-27, 2024-05-03, 2024-05-11, 2024-05-18, 2024-05-24, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-23, 2024-06-27, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-01, 2024-08-10, 2024-08-15, 2024-08-24, 2024-08-26, 2024-08-30, 2024-09-05, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-05, 2024-10-09, 2024-10-18, 2024-10-25, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-21, 2024-11-30, 2024-12-07, 2024-12-13, 2025-01-10, 2025-01-20, 2025-01-25, 2025-02-01, 2025-02-07, 2025-02-14, 2025-02-24, 2025-03-01, 2025-03-26, 2025-04-24, 2025-06-04, 2025-07-04, 2025-12-26, 2025-12-29, 2025-12-30, 2026-01-02, 2026-01-05, 2026-01-09, 2026-01-19, 2026-01-20, 2026-01-21, 2026-01-26, 2026-01-27, 2026-01-28, 2026-01-30, 2026-01-31, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16, 2026-03-02, 2026-03-03</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -3193,12 +3121,12 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2023-08-14, 2023-08-25, 2023-08-27, 2024-02-14, 2024-02-21, 2024-02-29, 2024-03-07, 2024-03-12, 2024-03-21, 2024-03-27, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-17, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-22, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-05, 2024-12-10, 2024-12-17, 2024-12-27, 2025-01-15, 2025-01-21, 2025-01-28, 2025-02-06, 2025-02-11, 2025-02-18, 2025-02-26, 2025-03-05, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-22, 2025-04-29, 2025-05-06, 2025-05-13, 2025-05-20, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-28, 2025-08-05, 2025-08-12, 2025-08-19, 2025-08-26, 2025-09-02, 2025-09-04, 2025-09-16, 2025-09-23, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-02, 2025-12-09, 2025-12-16, 2025-12-23, 2025-12-30, 2026-01-06, 2026-01-13, 2026-01-20, 2026-01-27, 2026-02-03, 2026-02-10, 2026-02-17, 2026-02-19, 2026-02-24, 2026-03-03, 2026-03-05</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-19, 2026-02-24</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2023-08-25, 2024-01-31, 2024-02-16, 2024-02-24, 2024-03-01, 2024-03-09, 2024-03-16, 2024-03-23, 2024-03-27, 2024-04-04, 2024-04-13, 2024-04-20, 2024-04-27, 2024-05-04, 2024-05-10, 2024-05-18, 2024-05-25, 2024-06-01, 2024-06-07, 2024-06-14, 2024-06-22, 2024-06-29, 2024-07-06, 2024-07-12, 2024-07-19, 2024-07-27, 2024-08-06, 2024-08-10, 2024-08-16, 2024-08-25, 2024-08-31, 2024-09-07, 2024-09-14, 2024-09-21, 2024-09-25, 2024-10-04, 2024-10-12, 2024-10-18, 2024-10-25, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-27, 2024-12-07, 2024-12-12, 2024-12-18, 2025-01-09, 2025-01-17, 2025-01-22, 2025-01-29, 2025-02-08, 2025-02-13, 2025-02-21, 2025-02-27, 2025-03-07, 2025-03-12, 2025-03-19, 2025-03-26, 2025-04-03, 2025-04-11, 2025-04-24, 2025-04-30, 2025-05-07, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-06, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-02, 2025-07-11, 2025-07-17, 2025-07-23, 2025-07-31, 2025-08-06, 2025-08-15, 2025-08-21, 2025-08-29, 2025-09-03, 2025-09-11, 2025-09-19, 2025-09-24, 2025-10-01, 2025-10-09, 2025-10-15, 2025-10-25, 2025-10-31, 2025-11-06, 2025-11-11, 2025-11-21, 2025-11-28, 2025-12-04, 2025-12-12, 2025-12-17, 2025-12-27, 2026-01-03, 2026-01-09, 2026-01-16, 2026-01-26, 2026-01-29, 2026-02-07, 2026-02-12, 2026-02-19, 2026-02-24, 2026-03-04, 2026-03-05</t>
+          <t>2026-02-07, 2026-02-12, 2026-02-19, 2026-02-24</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -3291,12 +3219,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2023-08-14, 2025-12-22, 2025-12-26, 2026-01-02, 2026-01-07, 2026-01-14, 2026-01-22, 2026-01-29, 2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25, 2026-03-04</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2025-12-26, 2026-01-02, 2026-01-08, 2026-01-16, 2026-01-22, 2026-01-30, 2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -3361,12 +3289,12 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2025-10-31, 2025-11-04, 2025-11-06, 2025-11-12, 2025-12-04, 2025-12-17, 2026-01-09, 2026-01-10, 2026-01-13, 2026-01-26, 2026-01-27, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-03-04, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-06, 2025-11-12, 2025-12-04, 2025-12-17, 2025-12-27, 2026-01-09, 2026-01-10, 2026-01-13, 2026-01-27, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-03-04, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -3457,12 +3385,12 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2023-06-07, 2023-06-14, 2023-06-21, 2023-06-29, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-27, 2023-08-03, 2023-08-09, 2023-08-16, 2023-08-24, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-26, 2023-10-05, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-16, 2023-11-22, 2023-11-29, 2023-12-07, 2023-12-13, 2023-12-27, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-02-01, 2024-02-07, 2024-02-15, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-10, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-30, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-03, 2024-09-11, 2024-09-18, 2024-09-25, 2024-10-02, 2024-10-09, 2024-10-16, 2024-10-23, 2024-10-28, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-27, 2024-12-04, 2024-12-12, 2024-12-20, 2025-01-08, 2025-01-15, 2025-01-22, 2025-01-30, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-05, 2025-03-11, 2025-03-20, 2025-03-27, 2025-04-02, 2025-04-09, 2025-04-24, 2025-04-30, 2025-05-07, 2025-05-14, 2025-05-22, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-09, 2025-07-16, 2025-07-23, 2025-07-31, 2025-08-08, 2025-08-13, 2025-08-20, 2025-08-28, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-25, 2025-10-02, 2025-10-22, 2025-11-01, 2025-11-12, 2025-11-19, 2025-11-27, 2025-12-04, 2025-12-10, 2025-12-18, 2026-01-14, 2026-01-22, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-21, 2023-07-28, 2023-08-03, 2023-08-10, 2023-08-18, 2023-08-24, 2023-08-31, 2023-09-07, 2023-09-14, 2023-09-21, 2023-09-28, 2023-10-06, 2023-10-12, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-09, 2023-11-17, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-28, 2024-01-04, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-02, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-20, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-12, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-25, 2025-05-03, 2025-05-08, 2025-05-15, 2025-05-24, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-04, 2025-07-10, 2025-07-18, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-10-02, 2025-10-22, 2025-11-01, 2025-11-12, 2025-11-13, 2025-11-21, 2025-11-27, 2025-12-04, 2025-12-12, 2025-12-18, 2026-01-15, 2026-01-22, 2026-01-30, 2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-05</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -3525,16 +3453,8 @@
       <c r="P38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>2023-03-09, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-19, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-09-01, 2023-09-07, 2023-09-14, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-21, 2023-10-28, 2023-11-03, 2023-11-10, 2023-11-17, 2024-08-06, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-29, 2024-12-06, 2024-12-13, 2024-12-23, 2024-12-27, 2025-01-10, 2025-01-17, 2025-02-07, 2025-02-14, 2025-02-28, 2025-03-07, 2025-03-17, 2025-03-21, 2025-04-09, 2025-05-17</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>2023-03-10, 2023-03-17, 2023-03-24, 2023-03-31, 2023-04-14, 2023-04-21, 2023-04-28, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-09, 2023-06-16, 2023-06-23, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-21, 2023-07-28, 2023-08-04, 2023-08-11, 2023-08-18, 2023-08-25, 2023-09-01, 2023-09-08, 2023-09-15, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-21, 2023-10-28, 2023-11-03, 2023-11-14, 2023-11-17, 2024-08-16, 2024-08-30, 2024-09-06, 2024-09-09, 2024-09-20, 2024-09-25, 2024-10-03, 2024-10-08, 2024-10-17, 2024-10-25, 2024-10-29, 2024-11-06, 2024-11-13, 2024-12-04, 2024-12-09, 2024-12-18, 2024-12-26, 2025-01-09, 2025-01-16, 2025-01-23, 2025-02-12, 2025-02-17, 2025-03-05, 2025-03-12, 2025-03-20, 2025-03-27, 2025-04-11</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="n">
@@ -3621,12 +3541,12 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2024-06-12, 2024-06-19, 2024-06-24, 2024-07-04, 2024-07-11, 2024-07-17, 2024-07-24, 2024-08-01, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-04, 2024-09-12, 2024-09-18, 2024-09-25, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-23, 2024-10-30, 2024-11-06, 2024-11-15, 2024-11-20, 2024-11-28, 2024-12-05, 2024-12-11, 2024-12-19, 2024-12-26, 2025-01-08, 2025-01-16, 2025-01-22, 2025-01-29, 2025-02-03, 2025-02-12, 2025-02-19, 2025-02-26, 2025-03-05, 2025-03-12, 2025-03-19, 2025-03-26, 2025-04-02, 2025-04-09, 2025-04-23, 2025-04-30, 2025-05-07, 2025-05-14, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-10, 2025-07-16, 2025-07-23, 2025-07-31, 2025-08-06, 2025-08-13, 2025-08-21, 2025-09-03, 2025-09-11, 2025-09-18, 2025-09-24, 2025-10-06, 2025-10-09, 2025-10-17, 2025-10-27, 2025-10-30, 2025-11-06, 2025-11-14, 2025-11-20, 2025-11-26, 2025-12-05, 2025-12-11, 2026-01-16, 2026-01-22, 2026-01-28, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-04</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2024-06-12, 2024-06-21, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-06, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-17, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-19, 2024-12-26, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-19, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-06, 2025-10-09, 2025-10-17, 2025-10-29, 2025-10-30, 2025-11-06, 2025-11-14, 2025-11-21, 2025-11-27, 2025-12-05, 2025-12-11, 2026-01-16, 2026-01-22, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -3723,12 +3643,12 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2024-12-12, 2024-12-21, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-22, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-02, 2025-05-08, 2025-05-16, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-20, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-15, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-29, 2025-12-05, 2025-12-11, 2025-12-19, 2026-01-17, 2026-01-22, 2026-01-29, 2026-02-05, 2026-02-14, 2026-02-20, 2026-02-24, 2026-03-05</t>
+          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-24</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2025-01-07, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-31, 2025-02-07, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-08, 2025-03-14, 2025-03-22, 2025-03-27, 2025-04-05, 2025-04-12, 2025-04-26, 2025-05-03, 2025-05-10, 2025-05-17, 2025-05-24, 2025-05-31, 2025-06-06, 2025-06-13, 2025-06-21, 2025-06-27, 2025-07-05, 2025-07-12, 2025-07-19, 2025-07-25, 2025-08-02, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-19, 2025-09-26, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-24, 2025-11-29, 2025-12-06, 2025-12-12, 2026-01-17, 2026-01-23, 2026-01-31, 2026-02-06, 2026-02-14, 2026-02-21, 2026-02-28, 2026-03-06</t>
+          <t>2026-02-06, 2026-02-14, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -3817,12 +3737,12 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2023-08-14, 2024-08-20, 2025-01-15, 2025-01-22, 2025-01-29, 2025-02-05, 2025-02-12, 2025-02-19, 2025-02-26, 2025-03-05, 2025-03-13, 2025-03-19, 2025-03-26, 2025-04-02, 2025-04-09, 2025-04-16, 2025-04-24, 2025-05-07, 2025-05-14, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-09, 2025-07-15, 2025-07-23, 2025-07-25, 2025-08-02, 2025-08-06, 2025-08-13, 2025-08-20, 2025-08-27, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-24, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-21, 2025-10-24, 2025-10-28, 2025-10-29, 2025-11-04, 2025-11-11, 2025-11-18, 2025-11-26, 2025-12-05, 2025-12-12, 2026-01-09, 2026-01-20, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2024-02-22, 2025-01-15, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-19, 2025-03-26, 2025-04-03, 2025-04-09, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-14, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-02, 2025-08-06, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-05, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-24, 2025-10-29, 2025-11-05, 2025-11-13, 2025-11-19, 2025-11-27, 2025-12-05, 2025-12-12, 2026-01-09, 2026-01-22, 2026-01-30, 2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27, 2026-03-06</t>
+          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -3967,16 +3887,8 @@
       <c r="P43" t="n">
         <v>4</v>
       </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="n">
@@ -4063,12 +3975,12 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2023-09-07, 2023-09-12, 2023-09-19, 2023-09-25, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-12, 2023-12-19, 2024-01-09, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-14, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-12, 2024-03-20, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-23, 2024-04-25, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-18, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-20, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2025-01-16, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-11, 2025-02-19, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-18, 2025-07-24, 2025-07-31, 2025-08-07, 2025-08-14, 2025-08-21, 2025-08-29, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-21, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2025-12-27, 2026-01-14, 2026-01-22, 2026-01-29, 2026-02-03, 2026-02-04, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05, 2026-03-12</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2023-09-07, 2023-09-12, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-23, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-15, 2024-02-21, 2024-02-29, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-10, 2024-04-17, 2024-04-24, 2024-05-02, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-21, 2024-07-25, 2024-07-31, 2024-08-08, 2024-08-15, 2024-08-21, 2024-08-28, 2024-09-04, 2024-09-11, 2024-09-19, 2024-09-25, 2024-10-02, 2024-10-11, 2024-10-16, 2024-10-23, 2024-10-30, 2024-11-06, 2024-11-13, 2024-11-20, 2024-11-28, 2024-12-04, 2024-12-11, 2025-01-10, 2025-01-16, 2025-01-22, 2025-01-29, 2025-02-05, 2025-02-12, 2025-02-19, 2025-02-28, 2025-03-07, 2025-03-20, 2025-03-21, 2025-03-28, 2025-04-05, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-09, 2025-05-15, 2025-05-23, 2025-05-30, 2025-06-07, 2025-06-13, 2025-06-26, 2025-06-27, 2025-07-04, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-22, 2025-09-26, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-24, 2025-11-28, 2025-12-05, 2025-12-12, 2025-12-19, 2025-12-27, 2026-01-14, 2026-01-24, 2026-02-02, 2026-02-03, 2026-02-09, 2026-02-18, 2026-02-21, 2026-03-03, 2026-03-06, 2026-03-16</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-18, 2026-02-21</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -4161,12 +4073,12 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2023-08-04, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-06, 2024-12-13, 2024-12-19, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-04, 2025-04-10, 2025-04-25, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-13, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2026-01-15, 2026-01-22, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-18, 2026-02-26, 2026-03-05, 2026-03-12, 2026-03-19</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2023-08-31, 2024-10-25, 2024-11-02, 2024-11-08, 2024-11-14, 2024-11-21, 2024-11-30, 2024-12-06, 2024-12-13, 2024-12-19, 2025-01-10, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-03-06, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-27, 2025-04-04, 2025-04-12, 2025-04-26, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-31, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-08-01, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-07, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2026-01-15, 2026-01-24, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-20, 2026-02-26, 2026-03-05, 2026-03-12</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -4259,12 +4171,12 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2023-08-01, 2023-08-29, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-05, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-22, 2025-04-29, 2025-05-08, 2025-05-13, 2025-05-20, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-30, 2025-08-05, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-02, 2025-09-09, 2025-09-16, 2025-09-23, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-22, 2025-10-29, 2025-11-04, 2025-11-12, 2025-11-19, 2025-11-25, 2025-12-02, 2026-01-19, 2026-01-20, 2026-01-27, 2026-02-03, 2026-02-11, 2026-02-18, 2026-02-24, 2026-03-03, 2026-03-10, 2026-03-17</t>
+          <t>2026-02-03, 2026-02-11, 2026-02-18, 2026-02-24</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2025-02-05, 2025-02-11, 2025-02-19, 2025-02-27, 2025-03-05, 2025-03-12, 2025-03-19, 2025-03-26, 2025-04-02, 2025-04-10, 2025-04-24, 2025-05-07, 2025-05-08, 2025-05-14, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-19, 2025-06-25, 2025-07-02, 2025-07-09, 2025-07-16, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-13, 2025-08-20, 2025-08-27, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-24, 2025-10-01, 2025-10-08, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-05, 2025-11-18, 2025-11-19, 2025-11-26, 2026-01-13, 2026-01-19, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-21, 2026-02-25, 2026-03-04, 2026-03-11, 2026-03-18</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-21, 2026-02-25</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -4353,12 +4265,12 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2023-02-02, 2023-02-09, 2023-02-16, 2023-02-23, 2023-03-02, 2023-03-09, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-19, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-08-31, 2023-09-07, 2023-09-14, 2023-09-21, 2023-09-28, 2023-10-05, 2023-10-12, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-09, 2023-11-16, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-13, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-16, 2024-05-24, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-06, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-29, 2024-12-05, 2024-12-12, 2024-12-19, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-14, 2025-02-21, 2025-02-27, 2025-03-06, 2025-03-14, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-02, 2025-05-09, 2025-05-15, 2025-05-23, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-11, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-07, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-07, 2025-11-13, 2025-11-20, 2025-11-28, 2025-12-04, 2025-12-12, 2025-12-20, 2026-01-15, 2026-01-22, 2026-02-21, 2026-02-26, 2026-03-06, 2026-03-14</t>
+          <t>2026-02-21, 2026-02-26</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2023-02-02, 2023-02-10, 2023-02-17, 2023-02-24, 2023-03-03, 2023-03-10, 2023-03-17, 2023-03-24, 2023-03-31, 2023-04-14, 2023-04-21, 2023-04-28, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-09, 2023-06-16, 2023-06-23, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-21, 2023-07-28, 2023-08-04, 2023-08-11, 2023-08-18, 2023-08-25, 2023-09-01, 2023-09-08, 2023-09-15, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-20, 2023-10-27, 2023-11-03, 2023-11-10, 2023-11-17, 2023-11-24, 2023-12-01, 2023-12-07, 2023-12-15, 2024-01-18, 2024-01-19, 2024-01-26, 2024-02-02, 2024-02-09, 2024-02-16, 2024-02-23, 2024-03-01, 2024-03-08, 2024-03-15, 2024-03-22, 2024-04-05, 2024-04-12, 2024-04-19, 2024-04-26, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-24, 2024-05-31, 2024-06-07, 2024-06-14, 2024-06-21, 2024-06-28, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-29, 2024-12-06, 2024-12-13, 2024-12-20, 2025-01-10, 2025-01-17, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-15, 2025-02-21, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-28, 2025-04-04, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-09, 2025-05-16, 2025-05-23, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-20, 2025-06-27, 2025-07-04, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-19, 2025-09-26, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-21, 2025-11-28, 2025-12-05, 2025-12-12, 2025-12-20, 2026-01-16, 2026-02-13, 2026-02-21, 2026-02-27, 2026-03-06, 2026-03-14</t>
+          <t>2026-02-13, 2026-02-21, 2026-02-27</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -4443,12 +4355,12 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2022-11-30, 2022-12-07, 2022-12-13, 2022-12-21, 2022-12-30, 2023-01-11, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-21, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-27, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-04, 2023-09-13, 2023-09-21, 2023-09-27, 2023-10-04, 2023-10-10, 2023-10-18, 2023-10-25, 2023-10-31, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-27, 2024-01-10, 2024-01-25, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-20, 2024-02-28, 2024-03-06, 2024-03-12, 2024-03-19, 2024-04-03, 2024-04-09, 2024-04-16, 2024-04-23, 2024-05-02, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-19, 2024-06-26, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-24, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-08-30, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-21, 2024-10-29, 2024-11-05, 2024-11-13, 2024-11-19, 2024-11-26, 2024-12-02, 2024-12-10, 2024-12-17, 2025-01-07, 2025-01-15, 2025-01-22, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-05, 2025-03-10, 2025-03-18, 2025-03-25, 2025-03-31, 2025-04-07, 2025-04-21, 2025-04-28, 2025-05-07, 2025-05-13, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-13, 2025-06-18, 2025-06-25, 2025-07-01, 2025-07-09, 2025-07-15, 2025-07-22, 2025-07-30, 2025-08-05, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-02, 2025-09-08, 2025-09-16, 2025-09-25, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-22, 2025-10-28, 2025-11-04, 2025-11-12, 2025-11-19, 2025-12-03, 2025-12-17, 2026-01-22, 2026-01-27, 2026-02-04, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-06, 2026-03-10, 2026-03-11, 2026-03-18</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2022-12-02, 2022-12-07, 2022-12-14, 2022-12-22, 2022-12-30, 2023-01-11, 2023-01-20, 2023-01-25, 2023-02-02, 2023-02-08, 2023-02-17, 2023-02-22, 2023-03-01, 2023-03-09, 2023-03-16, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-12, 2023-05-17, 2023-05-25, 2023-05-31, 2023-06-08, 2023-06-14, 2023-06-22, 2023-06-29, 2023-07-05, 2023-07-13, 2023-07-19, 2023-07-26, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-09-01, 2023-09-07, 2023-09-14, 2023-09-22, 2023-09-28, 2023-10-05, 2023-10-12, 2023-10-18, 2023-10-26, 2023-11-02, 2023-11-09, 2023-11-16, 2023-11-23, 2023-11-30, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-28, 2024-01-12, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-11, 2024-04-17, 2024-04-24, 2024-05-02, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-04, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-13, 2024-08-21, 2024-08-28, 2024-09-03, 2024-09-05, 2024-09-11, 2024-09-18, 2024-09-24, 2024-10-08, 2024-10-09, 2024-10-16, 2024-10-23, 2024-10-31, 2024-11-06, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-04, 2024-12-12, 2024-12-18, 2025-01-08, 2025-01-16, 2025-01-22, 2025-01-28, 2025-02-06, 2025-02-13, 2025-02-19, 2025-02-26, 2025-03-10, 2025-03-12, 2025-03-19, 2025-03-27, 2025-04-02, 2025-04-09, 2025-04-23, 2025-04-30, 2025-05-07, 2025-05-14, 2025-05-22, 2025-05-28, 2025-06-05, 2025-06-13, 2025-06-19, 2025-06-26, 2025-07-01, 2025-07-10, 2025-07-16, 2025-07-25, 2025-08-02, 2025-08-11, 2025-08-13, 2025-08-21, 2025-08-27, 2025-09-04, 2025-09-10, 2025-09-17, 2025-09-26, 2025-10-04, 2025-10-11, 2025-10-20, 2025-10-24, 2025-10-28, 2025-11-05, 2025-11-12, 2025-11-19, 2025-12-03, 2025-12-19, 2026-01-22, 2026-01-28, 2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27, 2026-03-06, 2026-03-11</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -4533,12 +4445,12 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2024-01-12, 2024-01-26, 2024-02-02, 2024-02-09, 2024-02-16, 2024-02-22, 2024-02-29, 2024-03-05, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-07, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-13, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-02, 2025-05-09, 2025-05-16, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-18, 2025-07-24, 2025-07-28, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-27, 2025-09-05, 2025-09-11, 2025-09-26, 2025-10-09, 2025-10-18, 2025-10-24, 2025-10-31, 2025-11-06, 2025-11-13, 2025-11-21, 2025-11-28, 2025-12-06, 2025-12-19, 2026-01-09, 2026-01-16, 2026-01-30, 2026-02-06, 2026-02-09, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-06, 2026-03-13</t>
+          <t>2026-02-06, 2026-02-09, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2024-01-26, 2024-01-30, 2024-02-02, 2024-02-09, 2024-02-16, 2024-02-23, 2024-03-01, 2024-03-08, 2024-03-15, 2024-03-22, 2024-04-05, 2024-04-12, 2024-04-19, 2024-04-26, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-24, 2024-05-31, 2024-06-07, 2024-06-14, 2024-06-21, 2024-06-28, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-29, 2024-12-06, 2024-12-13, 2025-01-10, 2025-01-17, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-14, 2025-02-21, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-28, 2025-04-04, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-09, 2025-05-16, 2025-05-23, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-20, 2025-06-27, 2025-07-04, 2025-07-10, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-28, 2025-09-05, 2025-09-12, 2025-09-26, 2025-10-11, 2025-10-18, 2025-10-24, 2025-10-31, 2025-11-06, 2025-11-21, 2025-11-28, 2025-12-06, 2025-12-19, 2026-01-09, 2026-01-23, 2026-01-30, 2026-02-06, 2026-02-09, 2026-02-12, 2026-02-20, 2026-02-27, 2026-03-06, 2026-03-14</t>
+          <t>2026-02-06, 2026-02-09, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -4623,12 +4535,12 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2025-10-01, 2025-10-15, 2025-10-29, 2025-11-12, 2025-11-19, 2025-12-03, 2026-01-07, 2026-01-21, 2026-02-04, 2026-02-11, 2026-02-23, 2026-03-02, 2026-03-09, 2026-03-18</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-23</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2025-10-01, 2025-10-29, 2025-11-12, 2025-11-14, 2025-12-03, 2026-01-21, 2026-02-04, 2026-02-11, 2026-02-23, 2026-03-09, 2026-03-18</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-23</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -4713,12 +4625,12 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2023-02-10, 2023-02-16, 2023-02-24, 2023-03-06, 2023-03-13, 2023-03-21, 2023-03-23, 2023-03-31, 2023-04-10, 2023-04-15, 2023-04-21, 2023-04-28, 2023-05-06, 2023-05-12, 2023-05-20, 2023-05-26, 2023-06-03, 2023-06-09, 2023-06-16, 2023-06-24, 2023-06-30, 2023-07-07, 2023-08-08, 2023-08-11, 2023-08-22, 2023-08-26, 2023-09-01, 2023-09-09, 2023-09-16, 2023-09-23, 2023-09-29, 2023-10-09, 2023-10-17, 2023-10-20, 2023-10-27, 2023-11-03, 2023-11-11, 2023-11-17, 2023-11-27, 2023-12-02, 2023-12-07, 2023-12-18, 2023-12-22, 2023-12-29, 2024-01-10, 2024-01-13, 2024-01-19, 2024-01-27, 2024-02-01, 2024-02-14, 2024-02-20, 2024-02-24, 2024-03-05, 2024-03-12, 2024-03-18, 2024-03-22, 2024-04-02, 2024-04-09, 2024-04-13, 2024-04-20, 2024-04-26, 2024-05-02, 2024-05-11, 2024-05-18, 2024-05-25, 2024-06-04, 2024-06-11, 2024-06-19, 2024-06-22, 2024-06-29, 2024-07-09, 2024-07-11, 2024-07-19, 2024-07-27, 2024-08-01, 2024-08-08, 2024-08-17, 2024-08-24, 2024-08-31, 2024-09-07, 2024-09-14, 2024-09-21, 2024-09-28, 2024-10-05, 2024-10-15, 2024-10-19, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-23, 2024-11-30, 2024-12-06, 2024-12-13, 2024-12-21, 2025-01-02, 2025-01-11, 2025-01-17, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-14, 2025-02-21, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-29, 2025-04-04, 2025-04-11, 2025-04-24, 2025-04-29, 2025-05-10, 2025-05-16, 2025-05-24, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-25, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-05, 2025-09-12, 2025-09-19, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-17, 2025-10-23, 2025-10-29, 2025-10-31, 2025-11-07, 2025-11-11, 2025-11-20, 2025-11-28, 2025-12-04, 2025-12-09, 2025-12-19, 2025-12-23, 2026-01-30, 2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28, 2026-03-07, 2026-03-14</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2023-02-13, 2023-02-16, 2023-02-24, 2023-02-27, 2023-03-06, 2023-03-13, 2023-03-22, 2023-03-27, 2023-04-03, 2023-04-10, 2023-04-17, 2023-04-24, 2023-05-02, 2023-05-08, 2023-05-15, 2023-05-23, 2023-05-29, 2023-06-03, 2023-06-05, 2023-06-13, 2023-06-20, 2023-06-26, 2023-07-04, 2023-07-13, 2023-08-09, 2023-08-14, 2023-08-24, 2023-08-28, 2023-09-04, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-02, 2023-10-10, 2023-10-19, 2023-10-24, 2023-10-31, 2023-11-08, 2023-11-16, 2023-11-20, 2023-11-28, 2023-12-05, 2023-12-11, 2023-12-19, 2023-12-26, 2024-01-02, 2024-01-10, 2024-01-16, 2024-01-24, 2024-01-30, 2024-02-06, 2024-02-14, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-12, 2024-03-19, 2024-03-26, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-26, 2024-04-30, 2024-05-07, 2024-05-18, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-22, 2024-06-25, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-10, 2024-08-17, 2024-08-24, 2024-08-31, 2024-09-07, 2024-09-14, 2024-09-21, 2024-09-28, 2024-10-05, 2024-10-15, 2024-10-19, 2024-10-25, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-30, 2024-12-07, 2024-12-14, 2024-12-21, 2025-01-02, 2025-01-11, 2025-01-17, 2025-01-25, 2025-01-31, 2025-02-07, 2025-02-15, 2025-02-21, 2025-02-28, 2025-03-09, 2025-03-14, 2025-03-21, 2025-03-29, 2025-04-05, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-10, 2025-05-16, 2025-05-24, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-20, 2025-06-28, 2025-07-05, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-02, 2025-08-08, 2025-08-16, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-20, 2025-09-27, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-29, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-21, 2025-11-29, 2025-12-06, 2025-12-12, 2025-12-20, 2026-01-23, 2026-01-30, 2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28, 2026-03-07, 2026-03-14</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -4803,12 +4715,12 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2023-08-01, 2023-08-28, 2023-10-03, 2023-11-29, 2024-01-25, 2024-01-31, 2024-02-01, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-20, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-04, 2024-10-10, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-29, 2024-12-06, 2024-12-13, 2024-12-20, 2024-12-27, 2025-01-03, 2025-01-10, 2025-01-17, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-14, 2025-02-21, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-28, 2025-04-04, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-09, 2025-05-16, 2025-05-23, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-20, 2025-06-27, 2025-07-04, 2025-07-10, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-19, 2025-09-26, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-21, 2025-11-28, 2025-12-05, 2025-12-12, 2026-01-16, 2026-01-19, 2026-01-20, 2026-01-23, 2026-01-30, 2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27, 2026-03-06, 2026-03-13</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2023-08-28, 2023-10-03, 2024-01-25, 2024-01-31, 2024-02-02, 2024-02-09, 2024-02-16, 2024-02-22, 2024-03-02, 2024-03-12, 2024-03-15, 2024-03-20, 2024-03-22, 2024-04-11, 2024-04-12, 2024-04-19, 2024-04-26, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-24, 2024-05-31, 2024-06-07, 2024-06-14, 2024-06-22, 2024-06-28, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-21, 2024-09-28, 2024-10-05, 2024-10-12, 2024-10-19, 2024-10-26, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-30, 2024-12-07, 2024-12-14, 2024-12-21, 2024-12-28, 2025-01-04, 2025-01-11, 2025-01-18, 2025-01-25, 2025-02-01, 2025-02-08, 2025-02-15, 2025-02-22, 2025-03-05, 2025-03-08, 2025-03-15, 2025-03-22, 2025-03-29, 2025-04-05, 2025-04-12, 2025-04-26, 2025-05-03, 2025-05-10, 2025-05-17, 2025-05-24, 2025-05-31, 2025-06-07, 2025-06-14, 2025-06-21, 2025-06-28, 2025-07-05, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-02, 2025-08-09, 2025-08-16, 2025-08-23, 2025-08-30, 2025-09-06, 2025-09-13, 2025-09-20, 2025-09-27, 2025-10-04, 2025-10-11, 2025-10-18, 2025-10-25, 2025-11-01, 2025-11-08, 2025-11-15, 2025-11-22, 2025-11-29, 2025-12-06, 2025-12-13, 2026-01-17, 2026-01-20, 2026-01-24, 2026-01-31, 2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28, 2026-03-07, 2026-03-14</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -4893,12 +4805,12 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2023-07-31, 2023-08-29, 2023-10-11, 2023-11-30, 2024-04-25, 2024-05-23, 2024-08-28, 2024-09-04, 2024-09-11, 2024-09-18, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-11-02, 2024-11-08, 2024-11-25, 2024-11-29, 2024-12-07, 2024-12-14, 2024-12-20, 2025-01-19, 2025-01-25, 2025-02-01, 2025-02-08, 2025-02-15, 2025-02-22, 2025-02-28, 2025-03-08, 2025-03-15, 2025-03-20, 2025-03-29, 2025-04-07, 2025-04-12, 2025-04-26, 2025-05-03, 2025-05-09, 2025-05-17, 2025-05-22, 2025-05-30, 2025-06-02, 2025-06-12, 2025-06-21, 2025-06-28, 2025-07-03, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-02, 2025-08-08, 2025-08-14, 2025-08-23, 2025-08-28, 2025-09-06, 2025-09-11, 2025-09-19, 2025-09-30, 2025-10-04, 2025-10-11, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-21, 2025-11-27, 2025-11-29, 2025-12-13, 2026-01-15, 2026-01-16, 2026-01-23, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05, 2026-03-13, 2026-03-19</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2023-10-11, 2024-04-25, 2024-05-23, 2024-08-28, 2024-08-29, 2024-09-06, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-11, 2024-10-18, 2024-10-27, 2024-11-02, 2024-11-08, 2024-11-25, 2024-11-29, 2024-12-07, 2024-12-14, 2024-12-20, 2025-01-19, 2025-01-25, 2025-02-01, 2025-02-08, 2025-02-16, 2025-02-22, 2025-03-08, 2025-03-18, 2025-03-22, 2025-03-29, 2025-04-07, 2025-04-13, 2025-04-30, 2025-05-08, 2025-05-12, 2025-05-21, 2025-05-29, 2025-06-01, 2025-06-07, 2025-06-14, 2025-06-21, 2025-06-28, 2025-07-05, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-02, 2025-08-09, 2025-08-16, 2025-08-23, 2025-08-30, 2025-09-06, 2025-09-12, 2025-09-19, 2025-10-01, 2025-10-04, 2025-10-11, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-15, 2025-11-21, 2025-11-29, 2025-12-06, 2025-12-19, 2026-01-16, 2026-01-23, 2026-01-30, 2026-02-05, 2026-02-13, 2026-02-21, 2026-02-27, 2026-03-06, 2026-03-13</t>
+          <t>2026-02-05, 2026-02-13, 2026-02-21, 2026-02-27</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -4983,12 +4895,12 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2025-08-14, 2025-08-21, 2025-08-28, 2025-09-05, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-03, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2026-01-08, 2026-01-15, 2026-01-22, 2026-01-29, 2026-02-04, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05, 2026-03-12</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2025-08-15, 2025-08-22, 2025-09-02, 2025-09-05, 2025-09-13, 2025-09-19, 2025-09-26, 2025-10-04, 2025-10-11, 2025-10-23, 2025-10-28, 2025-10-31, 2025-11-11, 2025-11-14, 2025-11-21, 2025-12-04, 2025-12-09, 2025-12-12, 2025-12-19, 2026-01-09, 2026-01-19, 2026-01-23, 2026-01-30, 2026-02-06, 2026-02-13, 2026-02-20, 2026-02-28, 2026-03-07, 2026-03-13</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-28</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         <v>4</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1030,10 +1030,10 @@
         <v>4</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         <v>4</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1236,10 +1236,10 @@
         <v>5</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="11">
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1384,10 +1384,10 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="X12" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="13">
@@ -1446,10 +1446,10 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="X13" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="14">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="X14" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="15">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1796,10 +1796,10 @@
         <v>4</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1898,10 +1898,10 @@
         <v>4</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1992,10 +1992,10 @@
         <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="X19" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="20">
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2206,10 +2206,10 @@
         <v>3</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="X22" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="23">
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2416,10 +2416,10 @@
         <v>4</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="26">
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2510,10 +2510,10 @@
         <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="X26" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="27">
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P28" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2670,10 +2670,10 @@
         <v>3</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X28" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="29">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2826,10 +2826,10 @@
         <v>3</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X30" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="31">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P32" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2982,10 +2982,10 @@
         <v>4</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="33">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P34" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -3146,10 +3146,10 @@
         <v>2</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="X34" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="35">
@@ -3212,10 +3212,10 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -3244,10 +3244,10 @@
         <v>4</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -3410,10 +3410,10 @@
         <v>4</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="38">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P39" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -3566,10 +3566,10 @@
         <v>4</v>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="40">
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P40" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -3668,10 +3668,10 @@
         <v>4</v>
       </c>
       <c r="W40" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="41">
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
         <v>2</v>
       </c>
       <c r="W41" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X41" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="42">
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P43" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -3968,10 +3968,10 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P44" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -4000,10 +4000,10 @@
         <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="X44" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="45">
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -4098,10 +4098,10 @@
         <v>4</v>
       </c>
       <c r="W45" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="X45" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="46">
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P46" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -4196,10 +4196,10 @@
         <v>3</v>
       </c>
       <c r="W46" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X46" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="47">
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P47" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -4290,10 +4290,10 @@
         <v>3</v>
       </c>
       <c r="W47" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="X47" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="48">
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P48" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -4380,10 +4380,10 @@
         <v>4</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X48" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="49">
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P49" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4470,10 +4470,10 @@
         <v>3</v>
       </c>
       <c r="W49" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X49" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="50">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P50" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         <v>2</v>
       </c>
       <c r="W50" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="X50" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="51">
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P51" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -4650,10 +4650,10 @@
         <v>4</v>
       </c>
       <c r="W51" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X51" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="52">
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
         <v>3</v>
       </c>
       <c r="W52" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X52" t="n">
-        <v>1</v>
+        <v>0.4285714285714285</v>
       </c>
     </row>
     <row r="53">
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -4830,10 +4830,10 @@
         <v>3</v>
       </c>
       <c r="W53" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X53" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="54">
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P54" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -4920,10 +4920,10 @@
         <v>4</v>
       </c>
       <c r="W54" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="X54" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         <v>4</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1030,10 +1030,10 @@
         <v>4</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         <v>4</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1236,10 +1236,10 @@
         <v>5</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1384,10 +1384,10 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="13">
@@ -1446,10 +1446,10 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="X13" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="14">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="X14" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1796,10 +1796,10 @@
         <v>4</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1898,10 +1898,10 @@
         <v>4</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1992,10 +1992,10 @@
         <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="X19" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2206,10 +2206,10 @@
         <v>3</v>
       </c>
       <c r="W22" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="23">
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2416,10 +2416,10 @@
         <v>4</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2510,10 +2510,10 @@
         <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="X26" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="27">
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2670,10 +2670,10 @@
         <v>3</v>
       </c>
       <c r="W28" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="29">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2826,10 +2826,10 @@
         <v>3</v>
       </c>
       <c r="W30" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="31">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2982,10 +2982,10 @@
         <v>4</v>
       </c>
       <c r="W32" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -3146,10 +3146,10 @@
         <v>2</v>
       </c>
       <c r="W34" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35">
@@ -3212,10 +3212,10 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -3244,10 +3244,10 @@
         <v>4</v>
       </c>
       <c r="W35" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -3410,10 +3410,10 @@
         <v>4</v>
       </c>
       <c r="W37" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P39" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -3566,10 +3566,10 @@
         <v>4</v>
       </c>
       <c r="W39" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P40" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -3668,10 +3668,10 @@
         <v>4</v>
       </c>
       <c r="W40" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="X40" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P41" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
         <v>2</v>
       </c>
       <c r="W41" t="n">
+        <v>1</v>
+      </c>
+      <c r="X41" t="n">
         <v>0.5</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="42">
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="P43" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -3968,10 +3968,10 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P44" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -4000,10 +4000,10 @@
         <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="X44" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="45">
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -4098,10 +4098,10 @@
         <v>4</v>
       </c>
       <c r="W45" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="X45" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -4196,10 +4196,10 @@
         <v>3</v>
       </c>
       <c r="W46" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X46" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="47">
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -4290,10 +4290,10 @@
         <v>3</v>
       </c>
       <c r="W47" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="X47" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="48">
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P48" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -4380,10 +4380,10 @@
         <v>4</v>
       </c>
       <c r="W48" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X48" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P49" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4470,10 +4470,10 @@
         <v>3</v>
       </c>
       <c r="W49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="50">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         <v>2</v>
       </c>
       <c r="W50" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="X50" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="51">
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -4650,10 +4650,10 @@
         <v>4</v>
       </c>
       <c r="W51" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X51" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P52" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
         <v>3</v>
       </c>
       <c r="W52" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X52" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="53">
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P53" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -4830,10 +4830,10 @@
         <v>3</v>
       </c>
       <c r="W53" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="54">
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P54" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -4920,10 +4920,10 @@
         <v>4</v>
       </c>
       <c r="W54" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="X54" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,7 +546,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PUERTA DORADA CRISTALINA</t>
+          <t>AMARETTO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -557,20 +557,16 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Germán Baquero</t>
+          <t>José Luis Suarez</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kelly Gutierrez</t>
+          <t>Abimael Padilla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>PUERTA DORADA</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>JUEVES</t>
@@ -583,12 +579,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>02:00:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -598,7 +594,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -614,7 +610,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-06, 2026-03-20, 2026-03-30</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -624,20 +620,20 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-20</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="U2" t="n">
         <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -648,7 +644,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AMARETTO</t>
+          <t>RIVERBAY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -664,14 +660,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Abimael Padilla</t>
+          <t>Orlando Iguaran</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>MARTES</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -681,7 +677,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -691,12 +687,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -707,22 +703,22 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -746,7 +742,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RIVERBAY</t>
+          <t>C DEL PARQUE TAYRONA APTOS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -757,44 +753,40 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>José Luis Suarez</t>
+          <t>Germán Baquero</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orlando Iguaran</t>
+          <t>Carlos Sandoval</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CIUDAD DEL PARQUE</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
+          <t xml:space="preserve">JUEVES </t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>02:00:00</t>
-        </is>
-      </c>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -805,35 +797,35 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-20</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-20</t>
         </is>
       </c>
       <c r="U4" t="n">
         <v>4</v>
       </c>
       <c r="V4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="5">
@@ -844,7 +836,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C DEL PARQUE TAYRONA APTOS</t>
+          <t>DIMARO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -855,40 +847,36 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Germán Baquero</t>
+          <t>José Luis Suarez</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Carlos Sandoval</t>
+          <t xml:space="preserve">Julio Curvelo </t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CIUDAD DEL PARQUE</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUEVES </t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -897,21 +885,37 @@
       <c r="P5" t="n">
         <v>4</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-10, 2026-03-11, 2026-03-18, 2026-03-31</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-11, 2026-03-20, 2026-03-31</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-11, 2026-03-18</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-11, 2026-03-20</t>
+        </is>
+      </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6">
@@ -922,7 +926,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DIMARO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -938,31 +942,31 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Julio Curvelo </t>
+          <t>Erich Camargo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
+          <t>VIERNES</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -971,21 +975,37 @@
       <c r="P6" t="n">
         <v>4</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-13, 2026-03-20</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-14</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-13, 2026-03-20</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-14</t>
+        </is>
+      </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -996,7 +1016,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>PARKSIDE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1012,31 +1032,31 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Erich Camargo</t>
+          <t>Ivan Barbosa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>MARTES</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -1045,21 +1065,37 @@
       <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09, 2026-03-18</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2026-03-09, 2026-03-18, 2026-03-21</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="8">
@@ -1070,7 +1106,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PARKSIDE</t>
+          <t>PUERTA DORADA ARRECIFE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1081,36 +1117,36 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>José Luis Suarez</t>
+          <t>Germán Baquero</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ivan Barbosa</t>
+          <t>Tatiana Navarro</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>LUNES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>MARTES</t>
+          <t>VIERNES</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1119,21 +1155,37 @@
       <c r="P8" t="n">
         <v>4</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
+        </is>
+      </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1144,7 +1196,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PUERTA DORADA ARRECIFE</t>
+          <t>PUERTA DORADA MARISMA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1160,54 +1212,70 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tatiana Navarro</t>
+          <t>Carlos Quiroz</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>VIERNES</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>SABADO</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-24, 2026-03-28</t>
         </is>
       </c>
       <c r="O9" t="n">
         <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-14, 2026-03-21</t>
+        </is>
+      </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="10">
@@ -1218,7 +1286,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PUERTA DORADA MARISMA</t>
+          <t>PUERTA DORADA NATURA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1234,54 +1302,70 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Carlos Quiroz</t>
+          <t>Lina Olarte</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SABADO</t>
+          <t>VIERNES</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-24, 2026-03-28</t>
-        </is>
-      </c>
       <c r="O10" t="n">
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-13, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-13, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-13, 2026-03-20</t>
+        </is>
+      </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11">
@@ -1292,7 +1376,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PUERTA DORADA NATURA</t>
+          <t>RIVERBLUE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1303,12 +1387,12 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Germán Baquero</t>
+          <t>José Luis Suarez</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lina Olarte</t>
+          <t>Jeeniffer Perez</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1341,21 +1425,37 @@
       <c r="P11" t="n">
         <v>4</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-13, 2026-03-21, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-13, 2026-03-21, 2026-03-27</t>
+        </is>
+      </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1366,7 +1466,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RIVERBLUE</t>
+          <t>PUERTA DORADA CRISTALINA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1377,28 +1477,40 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>José Luis Suarez</t>
+          <t>Germán Baquero</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeeniffer Perez</t>
+          <t>Kelly Gutierrez</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PUERTA DORADA</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
@@ -1415,21 +1527,127 @@
       <c r="P12" t="n">
         <v>4</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-06, 2026-03-20, 2026-03-30</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-20</t>
+        </is>
+      </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LOTE SEVILLA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Germán Baquero</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Danny Gerez</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-03-12, 2026-03-24, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2026-03-12, 2026-03-24, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -622,17 +622,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -715,22 +715,22 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>2026-03-05, 2026-03-11, 2026-03-19, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
           <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-05, 2026-03-11, 2026-03-19, 2026-03-25</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-14, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-20</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-14, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-20</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -828,13 +828,13 @@
         </is>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
         <v>3</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X4" t="n">
         <v>0.75</v>
@@ -899,35 +899,35 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-10, 2026-03-11, 2026-03-18, 2026-03-31</t>
+          <t>2026-03-06, 2026-03-10, 2026-03-11, 2026-03-20, 2026-03-31</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-11, 2026-03-20, 2026-03-31</t>
+          <t>2026-03-09, 2026-03-11, 2026-03-20, 2026-03-31</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-11, 2026-03-18</t>
+          <t>2026-03-06, 2026-03-11, 2026-03-20</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-11, 2026-03-20</t>
+          <t>2026-03-11, 2026-03-20</t>
         </is>
       </c>
       <c r="U5" t="n">
         <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W5" t="n">
         <v>0.75</v>
       </c>
       <c r="X5" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -989,7 +989,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20</t>
+          <t>2026-03-06, 2026-03-14</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20</t>
+          <t>2026-03-06, 2026-03-14</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
         <v>2</v>
       </c>
       <c r="W6" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="X6" t="n">
         <v>0.5</v>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-18</t>
+          <t>2026-03-09, 2026-03-18</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-03-09, 2026-03-18, 2026-03-21</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-18, 2026-03-21</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-21, 2026-03-30</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-21</t>
         </is>
       </c>
       <c r="U10" t="n">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-13, 2026-03-21, 2026-03-27</t>
+          <t>2026-03-07, 2026-03-13, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-13, 2026-03-21, 2026-03-27</t>
+          <t>2026-03-07, 2026-03-13, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
       <c r="U11" t="n">
@@ -1541,35 +1541,35 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-05, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-06, 2026-03-20, 2026-03-30</t>
+          <t>2026-03-03, 2026-03-11, 2026-03-20, 2026-03-30</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-05, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-20</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X12" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="13">

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,122 +429,122 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Gerente</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Director de obra</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ValidacionParametrización</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Cluster</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>DiaIntermedia</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>HorarioIntermedia</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>DiaSemanal</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>HorarioSemanal</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PosibleIntermedia</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>PosibleSemanal</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ConteoIntermedia</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ConteoSemanal</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>RealIntermedia</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RealSemanal</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>CoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>CoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>CumplimientoIntermedia</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>CumplimientoSemanal</t>
         </is>
@@ -618,22 +630,18 @@
           <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
-        </is>
-      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
         <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -807,22 +815,22 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
+          <t>2026-03-06, 2026-03-20</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>2026-03-06, 2026-03-14, 2026-03-20</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-03-06, 2026-03-14, 2026-03-20</t>
-        </is>
-      </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
         <v>3</v>
       </c>
       <c r="W4" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="X4" t="n">
         <v>0.75</v>
@@ -897,25 +905,25 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-11, 2026-03-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-03-11, 2026-03-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6">
@@ -987,22 +995,22 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>2026-03-06, 2026-03-14</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-03-06, 2026-03-14</t>
-        </is>
-      </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
         <v>2</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="X6" t="n">
         <v>0.5</v>
@@ -1165,24 +1173,20 @@
           <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
         <is>
           <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
-        </is>
-      </c>
       <c r="U8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>4</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
@@ -1262,20 +1266,20 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-14, 2026-03-21</t>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
       <c r="U9" t="n">
         <v>4</v>
       </c>
       <c r="V9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
